--- a/data/ECMB.MI.xlsx
+++ b/data/ECMB.MI.xlsx
@@ -20037,6 +20037,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="856">
+      <c r="A856" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B856" t="n">
+        <v>4400</v>
+      </c>
+      <c r="C856" t="n">
+        <v>6.19999980926514</v>
+      </c>
+      <c r="D856" t="n">
+        <v>6.09999990463257</v>
+      </c>
+      <c r="E856" t="n">
+        <v>6.19999980926514</v>
+      </c>
+      <c r="F856" t="n">
+        <v>6.09999990463257</v>
+      </c>
+      <c r="G856" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ECMB.MI.xlsx
+++ b/data/ECMB.MI.xlsx
@@ -20060,6 +20060,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="857">
+      <c r="A857" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B857" t="n">
+        <v>19600</v>
+      </c>
+      <c r="C857" t="n">
+        <v>6.30000019073486</v>
+      </c>
+      <c r="D857" t="n">
+        <v>6.05000019073486</v>
+      </c>
+      <c r="E857" t="n">
+        <v>6.05000019073486</v>
+      </c>
+      <c r="F857" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="G857" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ECMB.MI.xlsx
+++ b/data/ECMB.MI.xlsx
@@ -20083,6 +20083,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="858">
+      <c r="A858" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B858" t="n">
+        <v>11400</v>
+      </c>
+      <c r="C858" t="n">
+        <v>6.44999980926514</v>
+      </c>
+      <c r="D858" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="E858" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="F858" t="n">
+        <v>6.40000009536743</v>
+      </c>
+      <c r="G858" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ECMB.MI.xlsx
+++ b/data/ECMB.MI.xlsx
@@ -20106,6 +20106,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="859">
+      <c r="A859" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B859" t="n">
+        <v>40800</v>
+      </c>
+      <c r="C859" t="n">
+        <v>6.94999980926514</v>
+      </c>
+      <c r="D859" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E859" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F859" t="n">
+        <v>6.90000009536743</v>
+      </c>
+      <c r="G859" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ECMB.MI.xlsx
+++ b/data/ECMB.MI.xlsx
@@ -19947,22 +19947,22 @@
     </row>
     <row r="852">
       <c r="A852" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B852" t="n">
-        <v>1400</v>
+        <v>9800</v>
       </c>
       <c r="C852" t="n">
-        <v>6.09999990463257</v>
+        <v>6.30000019073486</v>
       </c>
       <c r="D852" t="n">
-        <v>6</v>
+        <v>5.90000009536743</v>
       </c>
       <c r="E852" t="n">
-        <v>6.09999990463257</v>
+        <v>6.15000009536743</v>
       </c>
       <c r="F852" t="n">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="G852" t="s">
         <v>7</v>
@@ -19970,22 +19970,22 @@
     </row>
     <row r="853">
       <c r="A853" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B853" t="n">
-        <v>11600</v>
+        <v>1400</v>
       </c>
       <c r="C853" t="n">
-        <v>6.40000009536743</v>
+        <v>6.09999990463257</v>
       </c>
       <c r="D853" t="n">
-        <v>5.90000009536743</v>
+        <v>6</v>
       </c>
       <c r="E853" t="n">
-        <v>5.90000009536743</v>
+        <v>6.09999990463257</v>
       </c>
       <c r="F853" t="n">
-        <v>6.40000009536743</v>
+        <v>6</v>
       </c>
       <c r="G853" t="s">
         <v>7</v>
@@ -19993,19 +19993,19 @@
     </row>
     <row r="854">
       <c r="A854" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B854" t="n">
-        <v>8600</v>
+        <v>11600</v>
       </c>
       <c r="C854" t="n">
         <v>6.40000009536743</v>
       </c>
       <c r="D854" t="n">
-        <v>6.09999990463257</v>
+        <v>5.90000009536743</v>
       </c>
       <c r="E854" t="n">
-        <v>6.30000019073486</v>
+        <v>5.90000009536743</v>
       </c>
       <c r="F854" t="n">
         <v>6.40000009536743</v>
@@ -20016,22 +20016,22 @@
     </row>
     <row r="855">
       <c r="A855" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B855" t="n">
-        <v>5800</v>
+        <v>8600</v>
       </c>
       <c r="C855" t="n">
-        <v>6.19999980926514</v>
+        <v>6.40000009536743</v>
       </c>
       <c r="D855" t="n">
-        <v>6.15000009536743</v>
+        <v>6.09999990463257</v>
       </c>
       <c r="E855" t="n">
-        <v>6.19999980926514</v>
+        <v>6.30000019073486</v>
       </c>
       <c r="F855" t="n">
-        <v>6.15000009536743</v>
+        <v>6.40000009536743</v>
       </c>
       <c r="G855" t="s">
         <v>7</v>
@@ -20039,22 +20039,22 @@
     </row>
     <row r="856">
       <c r="A856" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B856" t="n">
-        <v>4400</v>
+        <v>5800</v>
       </c>
       <c r="C856" t="n">
         <v>6.19999980926514</v>
       </c>
       <c r="D856" t="n">
-        <v>6.09999990463257</v>
+        <v>6.15000009536743</v>
       </c>
       <c r="E856" t="n">
         <v>6.19999980926514</v>
       </c>
       <c r="F856" t="n">
-        <v>6.09999990463257</v>
+        <v>6.15000009536743</v>
       </c>
       <c r="G856" t="s">
         <v>7</v>
@@ -20062,22 +20062,22 @@
     </row>
     <row r="857">
       <c r="A857" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B857" t="n">
-        <v>19600</v>
+        <v>4400</v>
       </c>
       <c r="C857" t="n">
-        <v>6.30000019073486</v>
+        <v>6.19999980926514</v>
       </c>
       <c r="D857" t="n">
-        <v>6.05000019073486</v>
+        <v>6.09999990463257</v>
       </c>
       <c r="E857" t="n">
-        <v>6.05000019073486</v>
+        <v>6.19999980926514</v>
       </c>
       <c r="F857" t="n">
-        <v>6.25</v>
+        <v>6.09999990463257</v>
       </c>
       <c r="G857" t="s">
         <v>7</v>
@@ -20085,22 +20085,22 @@
     </row>
     <row r="858">
       <c r="A858" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B858" t="n">
-        <v>11400</v>
+        <v>19600</v>
       </c>
       <c r="C858" t="n">
-        <v>6.44999980926514</v>
+        <v>6.30000019073486</v>
       </c>
       <c r="D858" t="n">
+        <v>6.05000019073486</v>
+      </c>
+      <c r="E858" t="n">
+        <v>6.05000019073486</v>
+      </c>
+      <c r="F858" t="n">
         <v>6.25</v>
-      </c>
-      <c r="E858" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="F858" t="n">
-        <v>6.40000009536743</v>
       </c>
       <c r="G858" t="s">
         <v>7</v>
@@ -20108,24 +20108,47 @@
     </row>
     <row r="859">
       <c r="A859" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B859" t="n">
-        <v>40800</v>
+        <v>11400</v>
       </c>
       <c r="C859" t="n">
+        <v>6.44999980926514</v>
+      </c>
+      <c r="D859" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="E859" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="F859" t="n">
+        <v>6.40000009536743</v>
+      </c>
+      <c r="G859" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="860">
+      <c r="A860" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B860" t="n">
+        <v>38600</v>
+      </c>
+      <c r="C860" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="D860" t="n">
+        <v>6.65000009536743</v>
+      </c>
+      <c r="E860" t="n">
         <v>6.94999980926514</v>
       </c>
-      <c r="D859" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="E859" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="F859" t="n">
-        <v>6.90000009536743</v>
-      </c>
-      <c r="G859" t="s">
+      <c r="F860" t="n">
+        <v>6.80000019073486</v>
+      </c>
+      <c r="G860" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ECMB.MI.xlsx
+++ b/data/ECMB.MI.xlsx
@@ -22787,6 +22787,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="863">
+      <c r="A863" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B863" t="n">
+        <v>7400</v>
+      </c>
+      <c r="C863" t="n">
+        <v>6.94999980926514</v>
+      </c>
+      <c r="D863" t="n">
+        <v>6.69999980926514</v>
+      </c>
+      <c r="E863" t="n">
+        <v>6.69999980926514</v>
+      </c>
+      <c r="F863" t="n">
+        <v>6.80000019073486</v>
+      </c>
+      <c r="G863" t="n">
+        <v>6.80000019073486</v>
+      </c>
+      <c r="H863" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ECMB.MI.xlsx
+++ b/data/ECMB.MI.xlsx
@@ -473,7 +473,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G4" t="n">
-        <v>8.25685882568359</v>
+        <v>8.25685787200928</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G5" t="n">
-        <v>8.17896270751953</v>
+        <v>8.17896366119385</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G7" t="n">
-        <v>8.0815954208374</v>
+        <v>8.08159446716309</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G9" t="n">
-        <v>8.17896270751953</v>
+        <v>8.17896366119385</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G10" t="n">
-        <v>8.17896270751953</v>
+        <v>8.17896366119385</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G11" t="n">
-        <v>8.14001655578613</v>
+        <v>8.14001560211182</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G15" t="n">
-        <v>7.82843637466431</v>
+        <v>7.82843685150146</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G16" t="n">
-        <v>7.90633153915405</v>
+        <v>7.90633106231689</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G18" t="n">
-        <v>7.94527864456177</v>
+        <v>7.94527912139893</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G19" t="n">
-        <v>7.94527864456177</v>
+        <v>7.94527912139893</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G23" t="n">
-        <v>7.77001523971558</v>
+        <v>7.77001571655273</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G27" t="n">
-        <v>7.94527864456177</v>
+        <v>7.94527912139893</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G28" t="n">
-        <v>7.94527864456177</v>
+        <v>7.94527912139893</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G29" t="n">
-        <v>7.77001523971558</v>
+        <v>7.77001571655273</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G30" t="n">
-        <v>7.77001523971558</v>
+        <v>7.77001571655273</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G35" t="n">
-        <v>8.0815954208374</v>
+        <v>8.08159446716309</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G37" t="n">
-        <v>8.0815954208374</v>
+        <v>8.08159446716309</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G38" t="n">
-        <v>8.17896270751953</v>
+        <v>8.17896366119385</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G40" t="n">
-        <v>8.29580593109131</v>
+        <v>8.29580688476562</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>8.5</v>
       </c>
       <c r="G41" t="n">
-        <v>8.27633190155029</v>
+        <v>8.27633285522461</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G42" t="n">
-        <v>8.17896270751953</v>
+        <v>8.17896366119385</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G54" t="n">
-        <v>8.78264904022217</v>
+        <v>8.78264999389648</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G55" t="n">
-        <v>8.86054420471191</v>
+        <v>8.86054515838623</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G58" t="n">
-        <v>8.66580677032471</v>
+        <v>8.66580581665039</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>8.92000007629395</v>
       </c>
       <c r="G59" t="n">
-        <v>8.68528079986572</v>
+        <v>8.68527984619141</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>8.5</v>
       </c>
       <c r="G62" t="n">
-        <v>8.27633190155029</v>
+        <v>8.27633285522461</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>8.5</v>
       </c>
       <c r="G63" t="n">
-        <v>8.27633190155029</v>
+        <v>8.27633285522461</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G66" t="n">
-        <v>8.0815954208374</v>
+        <v>8.08159446716309</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G67" t="n">
-        <v>7.90633153915405</v>
+        <v>7.90633106231689</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G69" t="n">
-        <v>7.94527864456177</v>
+        <v>7.94527912139893</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G72" t="n">
-        <v>7.94527864456177</v>
+        <v>7.94527912139893</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G75" t="n">
-        <v>8.0815954208374</v>
+        <v>8.08159446716309</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G76" t="n">
-        <v>7.75054216384888</v>
+        <v>7.75054168701172</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>7.76000022888184</v>
       </c>
       <c r="G79" t="n">
-        <v>7.55580472946167</v>
+        <v>7.55580520629883</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G81" t="n">
-        <v>7.65317296981812</v>
+        <v>7.65317344665527</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G82" t="n">
-        <v>7.65317296981812</v>
+        <v>7.65317344665527</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G85" t="n">
-        <v>7.82843637466431</v>
+        <v>7.82843685150146</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G86" t="n">
-        <v>7.82843637466431</v>
+        <v>7.82843685150146</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G87" t="n">
-        <v>7.80896377563477</v>
+        <v>7.80896329879761</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G88" t="n">
-        <v>7.82843637466431</v>
+        <v>7.82843685150146</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G91" t="n">
-        <v>7.63369989395142</v>
+        <v>7.63369941711426</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G95" t="n">
-        <v>7.80896377563477</v>
+        <v>7.80896329879761</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G96" t="n">
-        <v>7.80896377563477</v>
+        <v>7.80896329879761</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G101" t="n">
-        <v>7.84791088104248</v>
+        <v>7.84791040420532</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G105" t="n">
-        <v>7.94527864456177</v>
+        <v>7.94527912139893</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G110" t="n">
-        <v>7.47790908813477</v>
+        <v>7.47790956497192</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G111" t="n">
-        <v>7.47790908813477</v>
+        <v>7.47790956497192</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G119" t="n">
-        <v>8.0815954208374</v>
+        <v>8.08159446716309</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G120" t="n">
-        <v>8.0815954208374</v>
+        <v>8.08159446716309</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G121" t="n">
-        <v>7.90633153915405</v>
+        <v>7.90633106231689</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G122" t="n">
-        <v>7.90633153915405</v>
+        <v>7.90633106231689</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G124" t="n">
-        <v>8.04264736175537</v>
+        <v>8.04264831542969</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G129" t="n">
-        <v>7.82843637466431</v>
+        <v>7.82843685150146</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G130" t="n">
-        <v>7.82843637466431</v>
+        <v>7.82843685150146</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G134" t="n">
-        <v>7.75054216384888</v>
+        <v>7.75054168701172</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G135" t="n">
-        <v>7.94527864456177</v>
+        <v>7.94527912139893</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G136" t="n">
-        <v>7.94527864456177</v>
+        <v>7.94527912139893</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G141" t="n">
-        <v>7.82843637466431</v>
+        <v>7.82843685150146</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G142" t="n">
-        <v>7.82843637466431</v>
+        <v>7.82843685150146</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G154" t="n">
-        <v>7.45843601226807</v>
+        <v>7.45843553543091</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>7.78000020980835</v>
       </c>
       <c r="G157" t="n">
-        <v>7.57527875900269</v>
+        <v>7.57527828216553</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G168" t="n">
-        <v>6.42632818222046</v>
+        <v>6.42632865905762</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G178" t="n">
-        <v>7.08843517303467</v>
+        <v>7.08843564987183</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G179" t="n">
-        <v>7.08843517303467</v>
+        <v>7.08843564987183</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G180" t="n">
-        <v>6.83527660369873</v>
+        <v>6.83527708053589</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G182" t="n">
-        <v>6.73790836334229</v>
+        <v>6.73790788650513</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>7.78000020980835</v>
       </c>
       <c r="G197" t="n">
-        <v>7.57527875900269</v>
+        <v>7.57527828216553</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G199" t="n">
-        <v>7.28317260742188</v>
+        <v>7.28317213058472</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G200" t="n">
-        <v>7.12738275527954</v>
+        <v>7.1273832321167</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G202" t="n">
-        <v>6.54317045211792</v>
+        <v>6.54317092895508</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G203" t="n">
-        <v>6.54317045211792</v>
+        <v>6.54317092895508</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G204" t="n">
-        <v>6.54317045211792</v>
+        <v>6.54317092895508</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G206" t="n">
-        <v>6.27053880691528</v>
+        <v>6.27053928375244</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G207" t="n">
-        <v>6.2900128364563</v>
+        <v>6.29001235961914</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G210" t="n">
-        <v>6.42632818222046</v>
+        <v>6.42632865905762</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G214" t="n">
-        <v>5.97843265533447</v>
+        <v>5.97843313217163</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G215" t="n">
-        <v>5.9200119972229</v>
+        <v>5.92001152038574</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G216" t="n">
-        <v>5.9200119972229</v>
+        <v>5.92001152038574</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G227" t="n">
-        <v>5.74474859237671</v>
+        <v>5.74474811553955</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G229" t="n">
-        <v>5.62790632247925</v>
+        <v>5.62790584564209</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G232" t="n">
-        <v>5.74474859237671</v>
+        <v>5.74474811553955</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G233" t="n">
-        <v>5.74474859237671</v>
+        <v>5.74474811553955</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G235" t="n">
-        <v>5.74474859237671</v>
+        <v>5.74474811553955</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G236" t="n">
-        <v>5.74474859237671</v>
+        <v>5.74474811553955</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G249" t="n">
-        <v>5.74474859237671</v>
+        <v>5.74474811553955</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>5.5</v>
       </c>
       <c r="G251" t="n">
-        <v>5.35527420043945</v>
+        <v>5.35527372360229</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G253" t="n">
-        <v>5.06316804885864</v>
+        <v>5.06316757202148</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>5.5</v>
       </c>
       <c r="G259" t="n">
-        <v>5.35527420043945</v>
+        <v>5.35527372360229</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>5.25</v>
       </c>
       <c r="G260" t="n">
-        <v>5.11185264587402</v>
+        <v>5.11185216903687</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>5</v>
       </c>
       <c r="G261" t="n">
-        <v>4.86843061447144</v>
+        <v>4.86843109130859</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>5</v>
       </c>
       <c r="G262" t="n">
-        <v>4.86843061447144</v>
+        <v>4.86843109130859</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G263" t="n">
-        <v>5.25790500640869</v>
+        <v>5.25790548324585</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>5.25</v>
       </c>
       <c r="G265" t="n">
-        <v>5.11185264587402</v>
+        <v>5.11185216903687</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G267" t="n">
-        <v>5.25790500640869</v>
+        <v>5.25790548324585</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G268" t="n">
-        <v>5.4526424407959</v>
+        <v>5.45264196395874</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G271" t="n">
-        <v>5.4526424407959</v>
+        <v>5.45264196395874</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G272" t="n">
-        <v>5.4526424407959</v>
+        <v>5.45264196395874</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G274" t="n">
-        <v>5.55001068115234</v>
+        <v>5.5500111579895</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -22810,6 +22810,32 @@
         <v>6.80000019073486</v>
       </c>
       <c r="H863" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="864">
+      <c r="A864" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B864" t="n">
+        <v>5400</v>
+      </c>
+      <c r="C864" t="n">
+        <v>6.90000009536743</v>
+      </c>
+      <c r="D864" t="n">
+        <v>6.80000019073486</v>
+      </c>
+      <c r="E864" t="n">
+        <v>6.90000009536743</v>
+      </c>
+      <c r="F864" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="G864" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="H864" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/ECMB.MI.xlsx
+++ b/data/ECMB.MI.xlsx
@@ -22824,7 +22824,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="D864" t="n">
-        <v>6.80000019073486</v>
+        <v>6.75</v>
       </c>
       <c r="E864" t="n">
         <v>6.90000009536743</v>
@@ -22836,6 +22836,32 @@
         <v>6.75</v>
       </c>
       <c r="H864" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="865">
+      <c r="A865" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B865" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C865" t="n">
+        <v>6.84999990463257</v>
+      </c>
+      <c r="D865" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="E865" t="n">
+        <v>6.80000019073486</v>
+      </c>
+      <c r="F865" t="n">
+        <v>6.80000019073486</v>
+      </c>
+      <c r="G865" t="n">
+        <v>6.80000019073486</v>
+      </c>
+      <c r="H865" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/ECMB.MI.xlsx
+++ b/data/ECMB.MI.xlsx
@@ -473,7 +473,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G4" t="n">
-        <v>8.25685787200928</v>
+        <v>8.25685882568359</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G5" t="n">
-        <v>8.17896366119385</v>
+        <v>8.17896270751953</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G7" t="n">
-        <v>8.08159446716309</v>
+        <v>8.0815954208374</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G9" t="n">
-        <v>8.17896366119385</v>
+        <v>8.17896270751953</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G10" t="n">
-        <v>8.17896366119385</v>
+        <v>8.17896270751953</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G11" t="n">
-        <v>8.14001560211182</v>
+        <v>8.14001655578613</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G15" t="n">
-        <v>7.82843685150146</v>
+        <v>7.82843637466431</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G16" t="n">
-        <v>7.90633106231689</v>
+        <v>7.90633153915405</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G18" t="n">
-        <v>7.94527912139893</v>
+        <v>7.94527864456177</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G19" t="n">
-        <v>7.94527912139893</v>
+        <v>7.94527864456177</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G23" t="n">
-        <v>7.77001571655273</v>
+        <v>7.77001523971558</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G27" t="n">
-        <v>7.94527912139893</v>
+        <v>7.94527864456177</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G28" t="n">
-        <v>7.94527912139893</v>
+        <v>7.94527864456177</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G29" t="n">
-        <v>7.77001571655273</v>
+        <v>7.77001523971558</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G30" t="n">
-        <v>7.77001571655273</v>
+        <v>7.77001523971558</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G35" t="n">
-        <v>8.08159446716309</v>
+        <v>8.0815954208374</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G37" t="n">
-        <v>8.08159446716309</v>
+        <v>8.0815954208374</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G38" t="n">
-        <v>8.17896366119385</v>
+        <v>8.17896270751953</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G40" t="n">
-        <v>8.29580688476562</v>
+        <v>8.29580593109131</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>8.5</v>
       </c>
       <c r="G41" t="n">
-        <v>8.27633285522461</v>
+        <v>8.27633190155029</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G42" t="n">
-        <v>8.17896366119385</v>
+        <v>8.17896270751953</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G54" t="n">
-        <v>8.78264999389648</v>
+        <v>8.78264904022217</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G55" t="n">
-        <v>8.86054515838623</v>
+        <v>8.86054420471191</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G58" t="n">
-        <v>8.66580581665039</v>
+        <v>8.66580677032471</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>8.92000007629395</v>
       </c>
       <c r="G59" t="n">
-        <v>8.68527984619141</v>
+        <v>8.68528079986572</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>8.5</v>
       </c>
       <c r="G62" t="n">
-        <v>8.27633285522461</v>
+        <v>8.27633190155029</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>8.5</v>
       </c>
       <c r="G63" t="n">
-        <v>8.27633285522461</v>
+        <v>8.27633190155029</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G66" t="n">
-        <v>8.08159446716309</v>
+        <v>8.0815954208374</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G67" t="n">
-        <v>7.90633106231689</v>
+        <v>7.90633153915405</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G69" t="n">
-        <v>7.94527912139893</v>
+        <v>7.94527864456177</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G72" t="n">
-        <v>7.94527912139893</v>
+        <v>7.94527864456177</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G75" t="n">
-        <v>8.08159446716309</v>
+        <v>8.0815954208374</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G76" t="n">
-        <v>7.75054168701172</v>
+        <v>7.75054216384888</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>7.76000022888184</v>
       </c>
       <c r="G79" t="n">
-        <v>7.55580520629883</v>
+        <v>7.55580472946167</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G81" t="n">
-        <v>7.65317344665527</v>
+        <v>7.65317296981812</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G82" t="n">
-        <v>7.65317344665527</v>
+        <v>7.65317296981812</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G85" t="n">
-        <v>7.82843685150146</v>
+        <v>7.82843637466431</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G86" t="n">
-        <v>7.82843685150146</v>
+        <v>7.82843637466431</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G87" t="n">
-        <v>7.80896329879761</v>
+        <v>7.80896377563477</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G88" t="n">
-        <v>7.82843685150146</v>
+        <v>7.82843637466431</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G91" t="n">
-        <v>7.63369941711426</v>
+        <v>7.63369989395142</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G95" t="n">
-        <v>7.80896329879761</v>
+        <v>7.80896377563477</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G96" t="n">
-        <v>7.80896329879761</v>
+        <v>7.80896377563477</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G101" t="n">
-        <v>7.84791040420532</v>
+        <v>7.84791088104248</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G105" t="n">
-        <v>7.94527912139893</v>
+        <v>7.94527864456177</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G110" t="n">
-        <v>7.47790956497192</v>
+        <v>7.47790908813477</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G111" t="n">
-        <v>7.47790956497192</v>
+        <v>7.47790908813477</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G119" t="n">
-        <v>8.08159446716309</v>
+        <v>8.0815954208374</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G120" t="n">
-        <v>8.08159446716309</v>
+        <v>8.0815954208374</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G121" t="n">
-        <v>7.90633106231689</v>
+        <v>7.90633153915405</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G122" t="n">
-        <v>7.90633106231689</v>
+        <v>7.90633153915405</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G124" t="n">
-        <v>8.04264831542969</v>
+        <v>8.04264736175537</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G129" t="n">
-        <v>7.82843685150146</v>
+        <v>7.82843637466431</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G130" t="n">
-        <v>7.82843685150146</v>
+        <v>7.82843637466431</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G134" t="n">
-        <v>7.75054168701172</v>
+        <v>7.75054216384888</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G135" t="n">
-        <v>7.94527912139893</v>
+        <v>7.94527864456177</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G136" t="n">
-        <v>7.94527912139893</v>
+        <v>7.94527864456177</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G141" t="n">
-        <v>7.82843685150146</v>
+        <v>7.82843637466431</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G142" t="n">
-        <v>7.82843685150146</v>
+        <v>7.82843637466431</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G154" t="n">
-        <v>7.45843553543091</v>
+        <v>7.45843601226807</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>7.78000020980835</v>
       </c>
       <c r="G157" t="n">
-        <v>7.57527828216553</v>
+        <v>7.57527875900269</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G168" t="n">
-        <v>6.42632865905762</v>
+        <v>6.42632818222046</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G178" t="n">
-        <v>7.08843564987183</v>
+        <v>7.08843517303467</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G179" t="n">
-        <v>7.08843564987183</v>
+        <v>7.08843517303467</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G180" t="n">
-        <v>6.83527708053589</v>
+        <v>6.83527660369873</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G182" t="n">
-        <v>6.73790788650513</v>
+        <v>6.73790836334229</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>7.78000020980835</v>
       </c>
       <c r="G197" t="n">
-        <v>7.57527828216553</v>
+        <v>7.57527875900269</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G199" t="n">
-        <v>7.28317213058472</v>
+        <v>7.28317260742188</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G200" t="n">
-        <v>7.1273832321167</v>
+        <v>7.12738275527954</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G202" t="n">
-        <v>6.54317092895508</v>
+        <v>6.54317045211792</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G203" t="n">
-        <v>6.54317092895508</v>
+        <v>6.54317045211792</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G204" t="n">
-        <v>6.54317092895508</v>
+        <v>6.54317045211792</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G206" t="n">
-        <v>6.27053928375244</v>
+        <v>6.27053880691528</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G207" t="n">
-        <v>6.29001235961914</v>
+        <v>6.2900128364563</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G210" t="n">
-        <v>6.42632865905762</v>
+        <v>6.42632818222046</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G214" t="n">
-        <v>5.97843313217163</v>
+        <v>5.97843265533447</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G215" t="n">
-        <v>5.92001152038574</v>
+        <v>5.9200119972229</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G216" t="n">
-        <v>5.92001152038574</v>
+        <v>5.9200119972229</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G227" t="n">
-        <v>5.74474811553955</v>
+        <v>5.74474859237671</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G229" t="n">
-        <v>5.62790584564209</v>
+        <v>5.62790632247925</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G232" t="n">
-        <v>5.74474811553955</v>
+        <v>5.74474859237671</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G233" t="n">
-        <v>5.74474811553955</v>
+        <v>5.74474859237671</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G235" t="n">
-        <v>5.74474811553955</v>
+        <v>5.74474859237671</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G236" t="n">
-        <v>5.74474811553955</v>
+        <v>5.74474859237671</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G249" t="n">
-        <v>5.74474811553955</v>
+        <v>5.74474859237671</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>5.5</v>
       </c>
       <c r="G251" t="n">
-        <v>5.35527372360229</v>
+        <v>5.35527420043945</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G253" t="n">
-        <v>5.06316757202148</v>
+        <v>5.06316804885864</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>5.5</v>
       </c>
       <c r="G259" t="n">
-        <v>5.35527372360229</v>
+        <v>5.35527420043945</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>5.25</v>
       </c>
       <c r="G260" t="n">
-        <v>5.11185216903687</v>
+        <v>5.11185264587402</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>5</v>
       </c>
       <c r="G261" t="n">
-        <v>4.86843109130859</v>
+        <v>4.86843061447144</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>5</v>
       </c>
       <c r="G262" t="n">
-        <v>4.86843109130859</v>
+        <v>4.86843061447144</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G263" t="n">
-        <v>5.25790548324585</v>
+        <v>5.25790500640869</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>5.25</v>
       </c>
       <c r="G265" t="n">
-        <v>5.11185216903687</v>
+        <v>5.11185264587402</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G267" t="n">
-        <v>5.25790548324585</v>
+        <v>5.25790500640869</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G268" t="n">
-        <v>5.45264196395874</v>
+        <v>5.4526424407959</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G271" t="n">
-        <v>5.45264196395874</v>
+        <v>5.4526424407959</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G272" t="n">
-        <v>5.45264196395874</v>
+        <v>5.4526424407959</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G274" t="n">
-        <v>5.5500111579895</v>
+        <v>5.55001068115234</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -22862,6 +22862,32 @@
         <v>6.80000019073486</v>
       </c>
       <c r="H865" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="866">
+      <c r="A866" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B866" t="n">
+        <v>1600</v>
+      </c>
+      <c r="C866" t="n">
+        <v>6.84999990463257</v>
+      </c>
+      <c r="D866" t="n">
+        <v>6.84999990463257</v>
+      </c>
+      <c r="E866" t="n">
+        <v>6.84999990463257</v>
+      </c>
+      <c r="F866" t="n">
+        <v>6.84999990463257</v>
+      </c>
+      <c r="G866" t="n">
+        <v>6.84999990463257</v>
+      </c>
+      <c r="H866" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/ECMB.MI.xlsx
+++ b/data/ECMB.MI.xlsx
@@ -473,7 +473,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G4" t="n">
-        <v>8.25685882568359</v>
+        <v>8.25685787200928</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G5" t="n">
-        <v>8.17896270751953</v>
+        <v>8.17896366119385</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G7" t="n">
-        <v>8.0815954208374</v>
+        <v>8.08159446716309</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G9" t="n">
-        <v>8.17896270751953</v>
+        <v>8.17896366119385</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G10" t="n">
-        <v>8.17896270751953</v>
+        <v>8.17896366119385</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G11" t="n">
-        <v>8.14001655578613</v>
+        <v>8.14001560211182</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G15" t="n">
-        <v>7.82843637466431</v>
+        <v>7.82843685150146</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G16" t="n">
-        <v>7.90633153915405</v>
+        <v>7.90633106231689</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G18" t="n">
-        <v>7.94527864456177</v>
+        <v>7.94527912139893</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G19" t="n">
-        <v>7.94527864456177</v>
+        <v>7.94527912139893</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G23" t="n">
-        <v>7.77001523971558</v>
+        <v>7.77001571655273</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G27" t="n">
-        <v>7.94527864456177</v>
+        <v>7.94527912139893</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G28" t="n">
-        <v>7.94527864456177</v>
+        <v>7.94527912139893</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G29" t="n">
-        <v>7.77001523971558</v>
+        <v>7.77001571655273</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G30" t="n">
-        <v>7.77001523971558</v>
+        <v>7.77001571655273</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G35" t="n">
-        <v>8.0815954208374</v>
+        <v>8.08159446716309</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G37" t="n">
-        <v>8.0815954208374</v>
+        <v>8.08159446716309</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G38" t="n">
-        <v>8.17896270751953</v>
+        <v>8.17896366119385</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G40" t="n">
-        <v>8.29580593109131</v>
+        <v>8.29580688476562</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>8.5</v>
       </c>
       <c r="G41" t="n">
-        <v>8.27633190155029</v>
+        <v>8.27633285522461</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G42" t="n">
-        <v>8.17896270751953</v>
+        <v>8.17896366119385</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G54" t="n">
-        <v>8.78264904022217</v>
+        <v>8.78264999389648</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G55" t="n">
-        <v>8.86054420471191</v>
+        <v>8.86054515838623</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G58" t="n">
-        <v>8.66580677032471</v>
+        <v>8.66580581665039</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>8.92000007629395</v>
       </c>
       <c r="G59" t="n">
-        <v>8.68528079986572</v>
+        <v>8.68527984619141</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>8.5</v>
       </c>
       <c r="G62" t="n">
-        <v>8.27633190155029</v>
+        <v>8.27633285522461</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>8.5</v>
       </c>
       <c r="G63" t="n">
-        <v>8.27633190155029</v>
+        <v>8.27633285522461</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G66" t="n">
-        <v>8.0815954208374</v>
+        <v>8.08159446716309</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G67" t="n">
-        <v>7.90633153915405</v>
+        <v>7.90633106231689</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G69" t="n">
-        <v>7.94527864456177</v>
+        <v>7.94527912139893</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G72" t="n">
-        <v>7.94527864456177</v>
+        <v>7.94527912139893</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G75" t="n">
-        <v>8.0815954208374</v>
+        <v>8.08159446716309</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G76" t="n">
-        <v>7.75054216384888</v>
+        <v>7.75054168701172</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>7.76000022888184</v>
       </c>
       <c r="G79" t="n">
-        <v>7.55580472946167</v>
+        <v>7.55580520629883</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G81" t="n">
-        <v>7.65317296981812</v>
+        <v>7.65317344665527</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G82" t="n">
-        <v>7.65317296981812</v>
+        <v>7.65317344665527</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G85" t="n">
-        <v>7.82843637466431</v>
+        <v>7.82843685150146</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G86" t="n">
-        <v>7.82843637466431</v>
+        <v>7.82843685150146</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G87" t="n">
-        <v>7.80896377563477</v>
+        <v>7.80896329879761</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G88" t="n">
-        <v>7.82843637466431</v>
+        <v>7.82843685150146</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G91" t="n">
-        <v>7.63369989395142</v>
+        <v>7.63369941711426</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G95" t="n">
-        <v>7.80896377563477</v>
+        <v>7.80896329879761</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G96" t="n">
-        <v>7.80896377563477</v>
+        <v>7.80896329879761</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G101" t="n">
-        <v>7.84791088104248</v>
+        <v>7.84791040420532</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G105" t="n">
-        <v>7.94527864456177</v>
+        <v>7.94527912139893</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G110" t="n">
-        <v>7.47790908813477</v>
+        <v>7.47790956497192</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G111" t="n">
-        <v>7.47790908813477</v>
+        <v>7.47790956497192</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G119" t="n">
-        <v>8.0815954208374</v>
+        <v>8.08159446716309</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G120" t="n">
-        <v>8.0815954208374</v>
+        <v>8.08159446716309</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G121" t="n">
-        <v>7.90633153915405</v>
+        <v>7.90633106231689</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G122" t="n">
-        <v>7.90633153915405</v>
+        <v>7.90633106231689</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G124" t="n">
-        <v>8.04264736175537</v>
+        <v>8.04264831542969</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G129" t="n">
-        <v>7.82843637466431</v>
+        <v>7.82843685150146</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G130" t="n">
-        <v>7.82843637466431</v>
+        <v>7.82843685150146</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G134" t="n">
-        <v>7.75054216384888</v>
+        <v>7.75054168701172</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G135" t="n">
-        <v>7.94527864456177</v>
+        <v>7.94527912139893</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G136" t="n">
-        <v>7.94527864456177</v>
+        <v>7.94527912139893</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G141" t="n">
-        <v>7.82843637466431</v>
+        <v>7.82843685150146</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G142" t="n">
-        <v>7.82843637466431</v>
+        <v>7.82843685150146</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G154" t="n">
-        <v>7.45843601226807</v>
+        <v>7.45843553543091</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>7.78000020980835</v>
       </c>
       <c r="G157" t="n">
-        <v>7.57527875900269</v>
+        <v>7.57527828216553</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G168" t="n">
-        <v>6.42632818222046</v>
+        <v>6.42632865905762</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G178" t="n">
-        <v>7.08843517303467</v>
+        <v>7.08843564987183</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G179" t="n">
-        <v>7.08843517303467</v>
+        <v>7.08843564987183</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G180" t="n">
-        <v>6.83527660369873</v>
+        <v>6.83527708053589</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G182" t="n">
-        <v>6.73790836334229</v>
+        <v>6.73790788650513</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>7.78000020980835</v>
       </c>
       <c r="G197" t="n">
-        <v>7.57527875900269</v>
+        <v>7.57527828216553</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G199" t="n">
-        <v>7.28317260742188</v>
+        <v>7.28317213058472</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G200" t="n">
-        <v>7.12738275527954</v>
+        <v>7.1273832321167</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G202" t="n">
-        <v>6.54317045211792</v>
+        <v>6.54317092895508</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G203" t="n">
-        <v>6.54317045211792</v>
+        <v>6.54317092895508</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G204" t="n">
-        <v>6.54317045211792</v>
+        <v>6.54317092895508</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G206" t="n">
-        <v>6.27053880691528</v>
+        <v>6.27053928375244</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G207" t="n">
-        <v>6.2900128364563</v>
+        <v>6.29001235961914</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G210" t="n">
-        <v>6.42632818222046</v>
+        <v>6.42632865905762</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G214" t="n">
-        <v>5.97843265533447</v>
+        <v>5.97843313217163</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G215" t="n">
-        <v>5.9200119972229</v>
+        <v>5.92001152038574</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G216" t="n">
-        <v>5.9200119972229</v>
+        <v>5.92001152038574</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G227" t="n">
-        <v>5.74474859237671</v>
+        <v>5.74474811553955</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G229" t="n">
-        <v>5.62790632247925</v>
+        <v>5.62790584564209</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G232" t="n">
-        <v>5.74474859237671</v>
+        <v>5.74474811553955</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G233" t="n">
-        <v>5.74474859237671</v>
+        <v>5.74474811553955</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G235" t="n">
-        <v>5.74474859237671</v>
+        <v>5.74474811553955</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G236" t="n">
-        <v>5.74474859237671</v>
+        <v>5.74474811553955</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G249" t="n">
-        <v>5.74474859237671</v>
+        <v>5.74474811553955</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>5.5</v>
       </c>
       <c r="G251" t="n">
-        <v>5.35527420043945</v>
+        <v>5.35527372360229</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G253" t="n">
-        <v>5.06316804885864</v>
+        <v>5.06316757202148</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>5.5</v>
       </c>
       <c r="G259" t="n">
-        <v>5.35527420043945</v>
+        <v>5.35527372360229</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>5.25</v>
       </c>
       <c r="G260" t="n">
-        <v>5.11185264587402</v>
+        <v>5.11185216903687</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>5</v>
       </c>
       <c r="G261" t="n">
-        <v>4.86843061447144</v>
+        <v>4.86843109130859</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>5</v>
       </c>
       <c r="G262" t="n">
-        <v>4.86843061447144</v>
+        <v>4.86843109130859</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G263" t="n">
-        <v>5.25790500640869</v>
+        <v>5.25790548324585</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>5.25</v>
       </c>
       <c r="G265" t="n">
-        <v>5.11185264587402</v>
+        <v>5.11185216903687</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G267" t="n">
-        <v>5.25790500640869</v>
+        <v>5.25790548324585</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G268" t="n">
-        <v>5.4526424407959</v>
+        <v>5.45264196395874</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G271" t="n">
-        <v>5.4526424407959</v>
+        <v>5.45264196395874</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G272" t="n">
-        <v>5.4526424407959</v>
+        <v>5.45264196395874</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G274" t="n">
-        <v>5.55001068115234</v>
+        <v>5.5500111579895</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -22940,6 +22940,32 @@
         <v>6.90000009536743</v>
       </c>
       <c r="H868" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="869">
+      <c r="A869" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B869" t="n">
+        <v>8000</v>
+      </c>
+      <c r="C869" t="n">
+        <v>6.94999980926514</v>
+      </c>
+      <c r="D869" t="n">
+        <v>6.65000009536743</v>
+      </c>
+      <c r="E869" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="F869" t="n">
+        <v>6.80000019073486</v>
+      </c>
+      <c r="G869" t="n">
+        <v>6.80000019073486</v>
+      </c>
+      <c r="H869" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/ECMB.MI.xlsx
+++ b/data/ECMB.MI.xlsx
@@ -20421,8 +20421,31 @@
       <c r="E872" t="n">
         <v>6.69999980926514</v>
       </c>
-      <c r="F872"/>
+      <c r="F872" t="n">
+        <v>6.80000019073486</v>
+      </c>
       <c r="G872" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="873">
+      <c r="A873" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B873" t="n">
+        <v>3400</v>
+      </c>
+      <c r="C873" t="n">
+        <v>6.90000009536743</v>
+      </c>
+      <c r="D873" t="n">
+        <v>6.80000019073486</v>
+      </c>
+      <c r="E873" t="n">
+        <v>6.80000019073486</v>
+      </c>
+      <c r="F873"/>
+      <c r="G873" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ECMB.MI.xlsx
+++ b/data/ECMB.MI.xlsx
@@ -20444,8 +20444,31 @@
       <c r="E873" t="n">
         <v>6.80000019073486</v>
       </c>
-      <c r="F873"/>
+      <c r="F873" t="n">
+        <v>6.90000009536743</v>
+      </c>
       <c r="G873" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="874">
+      <c r="A874" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B874" t="n">
+        <v>4600</v>
+      </c>
+      <c r="C874" t="n">
+        <v>6.90000009536743</v>
+      </c>
+      <c r="D874" t="n">
+        <v>6.55000019073486</v>
+      </c>
+      <c r="E874" t="n">
+        <v>6.90000009536743</v>
+      </c>
+      <c r="F874"/>
+      <c r="G874" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ECMB.MI.xlsx
+++ b/data/ECMB.MI.xlsx
@@ -20467,8 +20467,31 @@
       <c r="E874" t="n">
         <v>6.90000009536743</v>
       </c>
-      <c r="F874"/>
+      <c r="F874" t="n">
+        <v>6.55000019073486</v>
+      </c>
       <c r="G874" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="875">
+      <c r="A875" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B875" t="n">
+        <v>1800</v>
+      </c>
+      <c r="C875" t="n">
+        <v>6.65000009536743</v>
+      </c>
+      <c r="D875" t="n">
+        <v>6.55000019073486</v>
+      </c>
+      <c r="E875" t="n">
+        <v>6.55000019073486</v>
+      </c>
+      <c r="F875"/>
+      <c r="G875" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ECMB.MI.xlsx
+++ b/data/ECMB.MI.xlsx
@@ -20490,8 +20490,31 @@
       <c r="E875" t="n">
         <v>6.55000019073486</v>
       </c>
-      <c r="F875"/>
+      <c r="F875" t="n">
+        <v>6.65000009536743</v>
+      </c>
       <c r="G875" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="876">
+      <c r="A876" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B876" t="n">
+        <v>400</v>
+      </c>
+      <c r="C876" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="D876" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="E876" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="F876"/>
+      <c r="G876" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ECMB.MI.xlsx
+++ b/data/ECMB.MI.xlsx
@@ -20520,6 +20520,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="877">
+      <c r="A877" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B877" t="n">
+        <v>6400</v>
+      </c>
+      <c r="C877" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="D877" t="n">
+        <v>6.55000019073486</v>
+      </c>
+      <c r="E877" t="n">
+        <v>6.59999990463257</v>
+      </c>
+      <c r="F877" t="n">
+        <v>6.69999980926514</v>
+      </c>
+      <c r="G877" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ECMB.MI.xlsx
+++ b/data/ECMB.MI.xlsx
@@ -473,7 +473,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G4" t="n">
-        <v>8.25685787200928</v>
+        <v>8.25685882568359</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G5" t="n">
-        <v>8.17896366119385</v>
+        <v>8.17896270751953</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G7" t="n">
-        <v>8.08159446716309</v>
+        <v>8.0815954208374</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G9" t="n">
-        <v>8.17896366119385</v>
+        <v>8.17896270751953</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G10" t="n">
-        <v>8.17896366119385</v>
+        <v>8.17896270751953</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G11" t="n">
-        <v>8.14001560211182</v>
+        <v>8.14001655578613</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G15" t="n">
-        <v>7.82843685150146</v>
+        <v>7.82843637466431</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G16" t="n">
-        <v>7.90633106231689</v>
+        <v>7.90633153915405</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G18" t="n">
-        <v>7.94527912139893</v>
+        <v>7.94527864456177</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G19" t="n">
-        <v>7.94527912139893</v>
+        <v>7.94527864456177</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G23" t="n">
-        <v>7.77001571655273</v>
+        <v>7.77001523971558</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G27" t="n">
-        <v>7.94527912139893</v>
+        <v>7.94527864456177</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G28" t="n">
-        <v>7.94527912139893</v>
+        <v>7.94527864456177</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G29" t="n">
-        <v>7.77001571655273</v>
+        <v>7.77001523971558</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G30" t="n">
-        <v>7.77001571655273</v>
+        <v>7.77001523971558</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G35" t="n">
-        <v>8.08159446716309</v>
+        <v>8.0815954208374</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G37" t="n">
-        <v>8.08159446716309</v>
+        <v>8.0815954208374</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G38" t="n">
-        <v>8.17896366119385</v>
+        <v>8.17896270751953</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G40" t="n">
-        <v>8.29580688476562</v>
+        <v>8.29580593109131</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>8.5</v>
       </c>
       <c r="G41" t="n">
-        <v>8.27633285522461</v>
+        <v>8.27633190155029</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G42" t="n">
-        <v>8.17896366119385</v>
+        <v>8.17896270751953</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G54" t="n">
-        <v>8.78264999389648</v>
+        <v>8.78264904022217</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G55" t="n">
-        <v>8.86054515838623</v>
+        <v>8.86054420471191</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G58" t="n">
-        <v>8.66580581665039</v>
+        <v>8.66580677032471</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>8.92000007629395</v>
       </c>
       <c r="G59" t="n">
-        <v>8.68527984619141</v>
+        <v>8.68528079986572</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>8.5</v>
       </c>
       <c r="G62" t="n">
-        <v>8.27633285522461</v>
+        <v>8.27633190155029</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>8.5</v>
       </c>
       <c r="G63" t="n">
-        <v>8.27633285522461</v>
+        <v>8.27633190155029</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G66" t="n">
-        <v>8.08159446716309</v>
+        <v>8.0815954208374</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G67" t="n">
-        <v>7.90633106231689</v>
+        <v>7.90633153915405</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G69" t="n">
-        <v>7.94527912139893</v>
+        <v>7.94527864456177</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G72" t="n">
-        <v>7.94527912139893</v>
+        <v>7.94527864456177</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G75" t="n">
-        <v>8.08159446716309</v>
+        <v>8.0815954208374</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G76" t="n">
-        <v>7.75054168701172</v>
+        <v>7.75054216384888</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>7.76000022888184</v>
       </c>
       <c r="G79" t="n">
-        <v>7.55580520629883</v>
+        <v>7.55580472946167</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G81" t="n">
-        <v>7.65317344665527</v>
+        <v>7.65317296981812</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G82" t="n">
-        <v>7.65317344665527</v>
+        <v>7.65317296981812</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G85" t="n">
-        <v>7.82843685150146</v>
+        <v>7.82843637466431</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G86" t="n">
-        <v>7.82843685150146</v>
+        <v>7.82843637466431</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G87" t="n">
-        <v>7.80896329879761</v>
+        <v>7.80896377563477</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G88" t="n">
-        <v>7.82843685150146</v>
+        <v>7.82843637466431</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G91" t="n">
-        <v>7.63369941711426</v>
+        <v>7.63369989395142</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G95" t="n">
-        <v>7.80896329879761</v>
+        <v>7.80896377563477</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G96" t="n">
-        <v>7.80896329879761</v>
+        <v>7.80896377563477</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G101" t="n">
-        <v>7.84791040420532</v>
+        <v>7.84791088104248</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G105" t="n">
-        <v>7.94527912139893</v>
+        <v>7.94527864456177</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G110" t="n">
-        <v>7.47790956497192</v>
+        <v>7.47790908813477</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G111" t="n">
-        <v>7.47790956497192</v>
+        <v>7.47790908813477</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G119" t="n">
-        <v>8.08159446716309</v>
+        <v>8.0815954208374</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G120" t="n">
-        <v>8.08159446716309</v>
+        <v>8.0815954208374</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G121" t="n">
-        <v>7.90633106231689</v>
+        <v>7.90633153915405</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G122" t="n">
-        <v>7.90633106231689</v>
+        <v>7.90633153915405</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G124" t="n">
-        <v>8.04264831542969</v>
+        <v>8.04264736175537</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G129" t="n">
-        <v>7.82843685150146</v>
+        <v>7.82843637466431</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G130" t="n">
-        <v>7.82843685150146</v>
+        <v>7.82843637466431</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G134" t="n">
-        <v>7.75054168701172</v>
+        <v>7.75054216384888</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G135" t="n">
-        <v>7.94527912139893</v>
+        <v>7.94527864456177</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G136" t="n">
-        <v>7.94527912139893</v>
+        <v>7.94527864456177</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G141" t="n">
-        <v>7.82843685150146</v>
+        <v>7.82843637466431</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G142" t="n">
-        <v>7.82843685150146</v>
+        <v>7.82843637466431</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G154" t="n">
-        <v>7.45843553543091</v>
+        <v>7.45843601226807</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>7.78000020980835</v>
       </c>
       <c r="G157" t="n">
-        <v>7.57527828216553</v>
+        <v>7.57527875900269</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G168" t="n">
-        <v>6.42632865905762</v>
+        <v>6.42632818222046</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G178" t="n">
-        <v>7.08843564987183</v>
+        <v>7.08843517303467</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G179" t="n">
-        <v>7.08843564987183</v>
+        <v>7.08843517303467</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G180" t="n">
-        <v>6.83527708053589</v>
+        <v>6.83527660369873</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G182" t="n">
-        <v>6.73790788650513</v>
+        <v>6.73790836334229</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>7.78000020980835</v>
       </c>
       <c r="G197" t="n">
-        <v>7.57527828216553</v>
+        <v>7.57527875900269</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G199" t="n">
-        <v>7.28317213058472</v>
+        <v>7.28317260742188</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G200" t="n">
-        <v>7.1273832321167</v>
+        <v>7.12738275527954</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G202" t="n">
-        <v>6.54317092895508</v>
+        <v>6.54317045211792</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G203" t="n">
-        <v>6.54317092895508</v>
+        <v>6.54317045211792</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G204" t="n">
-        <v>6.54317092895508</v>
+        <v>6.54317045211792</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G206" t="n">
-        <v>6.27053928375244</v>
+        <v>6.27053880691528</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G207" t="n">
-        <v>6.29001235961914</v>
+        <v>6.2900128364563</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G210" t="n">
-        <v>6.42632865905762</v>
+        <v>6.42632818222046</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G214" t="n">
-        <v>5.97843313217163</v>
+        <v>5.97843265533447</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G215" t="n">
-        <v>5.92001152038574</v>
+        <v>5.9200119972229</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G216" t="n">
-        <v>5.92001152038574</v>
+        <v>5.9200119972229</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G227" t="n">
-        <v>5.74474811553955</v>
+        <v>5.74474859237671</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G229" t="n">
-        <v>5.62790584564209</v>
+        <v>5.62790632247925</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G232" t="n">
-        <v>5.74474811553955</v>
+        <v>5.74474859237671</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G233" t="n">
-        <v>5.74474811553955</v>
+        <v>5.74474859237671</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G235" t="n">
-        <v>5.74474811553955</v>
+        <v>5.74474859237671</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G236" t="n">
-        <v>5.74474811553955</v>
+        <v>5.74474859237671</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G249" t="n">
-        <v>5.74474811553955</v>
+        <v>5.74474859237671</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>5.5</v>
       </c>
       <c r="G251" t="n">
-        <v>5.35527372360229</v>
+        <v>5.35527420043945</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G253" t="n">
-        <v>5.06316757202148</v>
+        <v>5.06316804885864</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>5.5</v>
       </c>
       <c r="G259" t="n">
-        <v>5.35527372360229</v>
+        <v>5.35527420043945</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>5.25</v>
       </c>
       <c r="G260" t="n">
-        <v>5.11185216903687</v>
+        <v>5.11185264587402</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>5</v>
       </c>
       <c r="G261" t="n">
-        <v>4.86843109130859</v>
+        <v>4.86843061447144</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>5</v>
       </c>
       <c r="G262" t="n">
-        <v>4.86843109130859</v>
+        <v>4.86843061447144</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G263" t="n">
-        <v>5.25790548324585</v>
+        <v>5.25790500640869</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>5.25</v>
       </c>
       <c r="G265" t="n">
-        <v>5.11185216903687</v>
+        <v>5.11185264587402</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G267" t="n">
-        <v>5.25790548324585</v>
+        <v>5.25790500640869</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G268" t="n">
-        <v>5.45264196395874</v>
+        <v>5.4526424407959</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G271" t="n">
-        <v>5.45264196395874</v>
+        <v>5.4526424407959</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G272" t="n">
-        <v>5.45264196395874</v>
+        <v>5.4526424407959</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G274" t="n">
-        <v>5.5500111579895</v>
+        <v>5.55001068115234</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -23226,6 +23226,32 @@
         <v>6.75</v>
       </c>
       <c r="H879" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="880">
+      <c r="A880" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B880" t="n">
+        <v>3200</v>
+      </c>
+      <c r="C880" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="D880" t="n">
+        <v>6.59999990463257</v>
+      </c>
+      <c r="E880" t="n">
+        <v>6.59999990463257</v>
+      </c>
+      <c r="F880" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="G880" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="H880" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/ECMB.MI.xlsx
+++ b/data/ECMB.MI.xlsx
@@ -485,7 +485,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G4" t="n">
-        <v>8.25685787200928</v>
+        <v>8.25685882568359</v>
       </c>
       <c r="H4" t="n">
         <v>7000</v>
@@ -514,7 +514,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G5" t="n">
-        <v>8.17896366119385</v>
+        <v>8.17896270751953</v>
       </c>
       <c r="H5" t="n">
         <v>1400</v>
@@ -572,7 +572,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G7" t="n">
-        <v>8.08159446716309</v>
+        <v>8.0815954208374</v>
       </c>
       <c r="H7" t="n">
         <v>4200</v>
@@ -630,7 +630,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G9" t="n">
-        <v>8.17896366119385</v>
+        <v>8.17896270751953</v>
       </c>
       <c r="H9" t="n">
         <v>200</v>
@@ -659,7 +659,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G10" t="n">
-        <v>8.17896366119385</v>
+        <v>8.17896270751953</v>
       </c>
       <c r="H10" t="n">
         <v>3600</v>
@@ -688,7 +688,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G11" t="n">
-        <v>8.14001560211182</v>
+        <v>8.14001655578613</v>
       </c>
       <c r="H11" t="n">
         <v>200</v>
@@ -804,7 +804,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G15" t="n">
-        <v>7.82843685150146</v>
+        <v>7.82843637466431</v>
       </c>
       <c r="H15" t="n">
         <v>2600</v>
@@ -833,7 +833,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G16" t="n">
-        <v>7.90633106231689</v>
+        <v>7.90633153915405</v>
       </c>
       <c r="H16" t="n">
         <v>6400</v>
@@ -891,7 +891,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G18" t="n">
-        <v>7.94527912139893</v>
+        <v>7.94527864456177</v>
       </c>
       <c r="H18" t="n">
         <v>2600</v>
@@ -920,7 +920,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G19" t="n">
-        <v>7.94527912139893</v>
+        <v>7.94527864456177</v>
       </c>
       <c r="H19" t="n">
         <v>600</v>
@@ -1036,7 +1036,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G23" t="n">
-        <v>7.77001571655273</v>
+        <v>7.77001523971558</v>
       </c>
       <c r="H23" t="n">
         <v>2600</v>
@@ -1152,7 +1152,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G27" t="n">
-        <v>7.94527912139893</v>
+        <v>7.94527864456177</v>
       </c>
       <c r="H27" t="n">
         <v>15200</v>
@@ -1181,7 +1181,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G28" t="n">
-        <v>7.94527912139893</v>
+        <v>7.94527864456177</v>
       </c>
       <c r="H28" t="n">
         <v>8200</v>
@@ -1210,7 +1210,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G29" t="n">
-        <v>7.77001571655273</v>
+        <v>7.77001523971558</v>
       </c>
       <c r="H29" t="n">
         <v>9000</v>
@@ -1239,7 +1239,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G30" t="n">
-        <v>7.77001571655273</v>
+        <v>7.77001523971558</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
@@ -1384,7 +1384,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G35" t="n">
-        <v>8.08159446716309</v>
+        <v>8.0815954208374</v>
       </c>
       <c r="H35" t="n">
         <v>1800</v>
@@ -1442,7 +1442,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G37" t="n">
-        <v>8.08159446716309</v>
+        <v>8.0815954208374</v>
       </c>
       <c r="H37" t="n">
         <v>3400</v>
@@ -1471,7 +1471,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G38" t="n">
-        <v>8.17896366119385</v>
+        <v>8.17896270751953</v>
       </c>
       <c r="H38" t="n">
         <v>14400</v>
@@ -1529,7 +1529,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G40" t="n">
-        <v>8.29580688476562</v>
+        <v>8.29580593109131</v>
       </c>
       <c r="H40" t="n">
         <v>4400</v>
@@ -1558,7 +1558,7 @@
         <v>8.5</v>
       </c>
       <c r="G41" t="n">
-        <v>8.27633285522461</v>
+        <v>8.27633190155029</v>
       </c>
       <c r="H41" t="n">
         <v>1200</v>
@@ -1587,7 +1587,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G42" t="n">
-        <v>8.17896366119385</v>
+        <v>8.17896270751953</v>
       </c>
       <c r="H42" t="n">
         <v>800</v>
@@ -1935,7 +1935,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G54" t="n">
-        <v>8.78264999389648</v>
+        <v>8.78264904022217</v>
       </c>
       <c r="H54" t="n">
         <v>4600</v>
@@ -1964,7 +1964,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G55" t="n">
-        <v>8.86054515838623</v>
+        <v>8.86054420471191</v>
       </c>
       <c r="H55" t="n">
         <v>6400</v>
@@ -2051,7 +2051,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G58" t="n">
-        <v>8.66580581665039</v>
+        <v>8.66580677032471</v>
       </c>
       <c r="H58" t="n">
         <v>2000</v>
@@ -2080,7 +2080,7 @@
         <v>8.92000007629395</v>
       </c>
       <c r="G59" t="n">
-        <v>8.68527984619141</v>
+        <v>8.68528079986572</v>
       </c>
       <c r="H59" t="n">
         <v>800</v>
@@ -2167,7 +2167,7 @@
         <v>8.5</v>
       </c>
       <c r="G62" t="n">
-        <v>8.27633285522461</v>
+        <v>8.27633190155029</v>
       </c>
       <c r="H62" t="n">
         <v>1600</v>
@@ -2196,7 +2196,7 @@
         <v>8.5</v>
       </c>
       <c r="G63" t="n">
-        <v>8.27633285522461</v>
+        <v>8.27633190155029</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
@@ -2283,7 +2283,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G66" t="n">
-        <v>8.08159446716309</v>
+        <v>8.0815954208374</v>
       </c>
       <c r="H66" t="n">
         <v>200</v>
@@ -2312,7 +2312,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G67" t="n">
-        <v>7.90633106231689</v>
+        <v>7.90633153915405</v>
       </c>
       <c r="H67" t="n">
         <v>3800</v>
@@ -2370,7 +2370,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G69" t="n">
-        <v>7.94527912139893</v>
+        <v>7.94527864456177</v>
       </c>
       <c r="H69" t="n">
         <v>2800</v>
@@ -2457,7 +2457,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G72" t="n">
-        <v>7.94527912139893</v>
+        <v>7.94527864456177</v>
       </c>
       <c r="H72" t="n">
         <v>1000</v>
@@ -2544,7 +2544,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G75" t="n">
-        <v>8.08159446716309</v>
+        <v>8.0815954208374</v>
       </c>
       <c r="H75" t="n">
         <v>2600</v>
@@ -2573,7 +2573,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G76" t="n">
-        <v>7.75054168701172</v>
+        <v>7.75054216384888</v>
       </c>
       <c r="H76" t="n">
         <v>4200</v>
@@ -2660,7 +2660,7 @@
         <v>7.76000022888184</v>
       </c>
       <c r="G79" t="n">
-        <v>7.55580520629883</v>
+        <v>7.55580472946167</v>
       </c>
       <c r="H79" t="n">
         <v>200</v>
@@ -2718,7 +2718,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G81" t="n">
-        <v>7.65317344665527</v>
+        <v>7.65317296981812</v>
       </c>
       <c r="H81" t="n">
         <v>400</v>
@@ -2747,7 +2747,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G82" t="n">
-        <v>7.65317344665527</v>
+        <v>7.65317296981812</v>
       </c>
       <c r="H82" t="n">
         <v>0</v>
@@ -2834,7 +2834,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G85" t="n">
-        <v>7.82843685150146</v>
+        <v>7.82843637466431</v>
       </c>
       <c r="H85" t="n">
         <v>200</v>
@@ -2863,7 +2863,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G86" t="n">
-        <v>7.82843685150146</v>
+        <v>7.82843637466431</v>
       </c>
       <c r="H86" t="n">
         <v>200</v>
@@ -2892,7 +2892,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G87" t="n">
-        <v>7.80896329879761</v>
+        <v>7.80896377563477</v>
       </c>
       <c r="H87" t="n">
         <v>2000</v>
@@ -2921,7 +2921,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G88" t="n">
-        <v>7.82843685150146</v>
+        <v>7.82843637466431</v>
       </c>
       <c r="H88" t="n">
         <v>2400</v>
@@ -3008,7 +3008,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G91" t="n">
-        <v>7.63369941711426</v>
+        <v>7.63369989395142</v>
       </c>
       <c r="H91" t="n">
         <v>800</v>
@@ -3124,7 +3124,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G95" t="n">
-        <v>7.80896329879761</v>
+        <v>7.80896377563477</v>
       </c>
       <c r="H95" t="n">
         <v>200</v>
@@ -3153,7 +3153,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G96" t="n">
-        <v>7.80896329879761</v>
+        <v>7.80896377563477</v>
       </c>
       <c r="H96" t="n">
         <v>0</v>
@@ -3298,7 +3298,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G101" t="n">
-        <v>7.84791040420532</v>
+        <v>7.84791088104248</v>
       </c>
       <c r="H101" t="n">
         <v>200</v>
@@ -3414,7 +3414,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G105" t="n">
-        <v>7.94527912139893</v>
+        <v>7.94527864456177</v>
       </c>
       <c r="H105" t="n">
         <v>1000</v>
@@ -3559,7 +3559,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G110" t="n">
-        <v>7.47790956497192</v>
+        <v>7.47790908813477</v>
       </c>
       <c r="H110" t="n">
         <v>1600</v>
@@ -3588,7 +3588,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G111" t="n">
-        <v>7.47790956497192</v>
+        <v>7.47790908813477</v>
       </c>
       <c r="H111" t="n">
         <v>0</v>
@@ -3820,7 +3820,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G119" t="n">
-        <v>8.08159446716309</v>
+        <v>8.0815954208374</v>
       </c>
       <c r="H119" t="n">
         <v>400</v>
@@ -3849,7 +3849,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G120" t="n">
-        <v>8.08159446716309</v>
+        <v>8.0815954208374</v>
       </c>
       <c r="H120" t="n">
         <v>0</v>
@@ -3878,7 +3878,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G121" t="n">
-        <v>7.90633106231689</v>
+        <v>7.90633153915405</v>
       </c>
       <c r="H121" t="n">
         <v>600</v>
@@ -3907,7 +3907,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G122" t="n">
-        <v>7.90633106231689</v>
+        <v>7.90633153915405</v>
       </c>
       <c r="H122" t="n">
         <v>0</v>
@@ -3965,7 +3965,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G124" t="n">
-        <v>8.04264831542969</v>
+        <v>8.04264736175537</v>
       </c>
       <c r="H124" t="n">
         <v>1600</v>
@@ -4110,7 +4110,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G129" t="n">
-        <v>7.82843685150146</v>
+        <v>7.82843637466431</v>
       </c>
       <c r="H129" t="n">
         <v>200</v>
@@ -4139,7 +4139,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G130" t="n">
-        <v>7.82843685150146</v>
+        <v>7.82843637466431</v>
       </c>
       <c r="H130" t="n">
         <v>0</v>
@@ -4255,7 +4255,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G134" t="n">
-        <v>7.75054168701172</v>
+        <v>7.75054216384888</v>
       </c>
       <c r="H134" t="n">
         <v>200</v>
@@ -4284,7 +4284,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G135" t="n">
-        <v>7.94527912139893</v>
+        <v>7.94527864456177</v>
       </c>
       <c r="H135" t="n">
         <v>800</v>
@@ -4313,7 +4313,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G136" t="n">
-        <v>7.94527912139893</v>
+        <v>7.94527864456177</v>
       </c>
       <c r="H136" t="n">
         <v>0</v>
@@ -4458,7 +4458,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G141" t="n">
-        <v>7.82843685150146</v>
+        <v>7.82843637466431</v>
       </c>
       <c r="H141" t="n">
         <v>600</v>
@@ -4487,7 +4487,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G142" t="n">
-        <v>7.82843685150146</v>
+        <v>7.82843637466431</v>
       </c>
       <c r="H142" t="n">
         <v>0</v>
@@ -4835,7 +4835,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G154" t="n">
-        <v>7.45843553543091</v>
+        <v>7.45843601226807</v>
       </c>
       <c r="H154" t="n">
         <v>400</v>
@@ -4922,7 +4922,7 @@
         <v>7.78000020980835</v>
       </c>
       <c r="G157" t="n">
-        <v>7.57527828216553</v>
+        <v>7.57527875900269</v>
       </c>
       <c r="H157" t="n">
         <v>600</v>
@@ -5241,7 +5241,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G168" t="n">
-        <v>6.42632865905762</v>
+        <v>6.42632818222046</v>
       </c>
       <c r="H168" t="n">
         <v>15400</v>
@@ -5531,7 +5531,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G178" t="n">
-        <v>7.08843564987183</v>
+        <v>7.08843517303467</v>
       </c>
       <c r="H178" t="n">
         <v>1000</v>
@@ -5560,7 +5560,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G179" t="n">
-        <v>7.08843564987183</v>
+        <v>7.08843517303467</v>
       </c>
       <c r="H179" t="n">
         <v>200</v>
@@ -5589,7 +5589,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G180" t="n">
-        <v>6.83527708053589</v>
+        <v>6.83527660369873</v>
       </c>
       <c r="H180" t="n">
         <v>4400</v>
@@ -5647,7 +5647,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G182" t="n">
-        <v>6.73790788650513</v>
+        <v>6.73790836334229</v>
       </c>
       <c r="H182" t="n">
         <v>800</v>
@@ -6082,7 +6082,7 @@
         <v>7.78000020980835</v>
       </c>
       <c r="G197" t="n">
-        <v>7.57527828216553</v>
+        <v>7.57527875900269</v>
       </c>
       <c r="H197" t="n">
         <v>3000</v>
@@ -6140,7 +6140,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G199" t="n">
-        <v>7.28317213058472</v>
+        <v>7.28317260742188</v>
       </c>
       <c r="H199" t="n">
         <v>2200</v>
@@ -6169,7 +6169,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G200" t="n">
-        <v>7.1273832321167</v>
+        <v>7.12738275527954</v>
       </c>
       <c r="H200" t="n">
         <v>3000</v>
@@ -6227,7 +6227,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G202" t="n">
-        <v>6.54317092895508</v>
+        <v>6.54317045211792</v>
       </c>
       <c r="H202" t="n">
         <v>1600</v>
@@ -6256,7 +6256,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G203" t="n">
-        <v>6.54317092895508</v>
+        <v>6.54317045211792</v>
       </c>
       <c r="H203" t="n">
         <v>3000</v>
@@ -6285,7 +6285,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G204" t="n">
-        <v>6.54317092895508</v>
+        <v>6.54317045211792</v>
       </c>
       <c r="H204" t="n">
         <v>0</v>
@@ -6343,7 +6343,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G206" t="n">
-        <v>6.27053928375244</v>
+        <v>6.27053880691528</v>
       </c>
       <c r="H206" t="n">
         <v>10600</v>
@@ -6372,7 +6372,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G207" t="n">
-        <v>6.29001235961914</v>
+        <v>6.2900128364563</v>
       </c>
       <c r="H207" t="n">
         <v>2200</v>
@@ -6459,7 +6459,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G210" t="n">
-        <v>6.42632865905762</v>
+        <v>6.42632818222046</v>
       </c>
       <c r="H210" t="n">
         <v>4200</v>
@@ -6575,7 +6575,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G214" t="n">
-        <v>5.97843313217163</v>
+        <v>5.97843265533447</v>
       </c>
       <c r="H214" t="n">
         <v>7800</v>
@@ -6604,7 +6604,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G215" t="n">
-        <v>5.92001152038574</v>
+        <v>5.9200119972229</v>
       </c>
       <c r="H215" t="n">
         <v>10000</v>
@@ -6633,7 +6633,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G216" t="n">
-        <v>5.92001152038574</v>
+        <v>5.9200119972229</v>
       </c>
       <c r="H216" t="n">
         <v>8200</v>
@@ -6952,7 +6952,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G227" t="n">
-        <v>5.74474811553955</v>
+        <v>5.74474859237671</v>
       </c>
       <c r="H227" t="n">
         <v>200</v>
@@ -7010,7 +7010,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G229" t="n">
-        <v>5.62790584564209</v>
+        <v>5.62790632247925</v>
       </c>
       <c r="H229" t="n">
         <v>11400</v>
@@ -7097,7 +7097,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G232" t="n">
-        <v>5.74474811553955</v>
+        <v>5.74474859237671</v>
       </c>
       <c r="H232" t="n">
         <v>200</v>
@@ -7126,7 +7126,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G233" t="n">
-        <v>5.74474811553955</v>
+        <v>5.74474859237671</v>
       </c>
       <c r="H233" t="n">
         <v>5800</v>
@@ -7184,7 +7184,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G235" t="n">
-        <v>5.74474811553955</v>
+        <v>5.74474859237671</v>
       </c>
       <c r="H235" t="n">
         <v>600</v>
@@ -7213,7 +7213,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G236" t="n">
-        <v>5.74474811553955</v>
+        <v>5.74474859237671</v>
       </c>
       <c r="H236" t="n">
         <v>0</v>
@@ -7590,7 +7590,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G249" t="n">
-        <v>5.74474811553955</v>
+        <v>5.74474859237671</v>
       </c>
       <c r="H249" t="n">
         <v>400</v>
@@ -7648,7 +7648,7 @@
         <v>5.5</v>
       </c>
       <c r="G251" t="n">
-        <v>5.35527372360229</v>
+        <v>5.35527420043945</v>
       </c>
       <c r="H251" t="n">
         <v>3400</v>
@@ -7706,7 +7706,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G253" t="n">
-        <v>5.06316757202148</v>
+        <v>5.06316804885864</v>
       </c>
       <c r="H253" t="n">
         <v>4000</v>
@@ -7880,7 +7880,7 @@
         <v>5.5</v>
       </c>
       <c r="G259" t="n">
-        <v>5.35527372360229</v>
+        <v>5.35527420043945</v>
       </c>
       <c r="H259" t="n">
         <v>200</v>
@@ -7909,7 +7909,7 @@
         <v>5.25</v>
       </c>
       <c r="G260" t="n">
-        <v>5.11185216903687</v>
+        <v>5.11185264587402</v>
       </c>
       <c r="H260" t="n">
         <v>16800</v>
@@ -7938,7 +7938,7 @@
         <v>5</v>
       </c>
       <c r="G261" t="n">
-        <v>4.86843109130859</v>
+        <v>4.86843061447144</v>
       </c>
       <c r="H261" t="n">
         <v>10600</v>
@@ -7967,7 +7967,7 @@
         <v>5</v>
       </c>
       <c r="G262" t="n">
-        <v>4.86843109130859</v>
+        <v>4.86843061447144</v>
       </c>
       <c r="H262" t="n">
         <v>15600</v>
@@ -7996,7 +7996,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G263" t="n">
-        <v>5.25790548324585</v>
+        <v>5.25790500640869</v>
       </c>
       <c r="H263" t="n">
         <v>35800</v>
@@ -8054,7 +8054,7 @@
         <v>5.25</v>
       </c>
       <c r="G265" t="n">
-        <v>5.11185216903687</v>
+        <v>5.11185264587402</v>
       </c>
       <c r="H265" t="n">
         <v>77400</v>
@@ -8112,7 +8112,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G267" t="n">
-        <v>5.25790548324585</v>
+        <v>5.25790500640869</v>
       </c>
       <c r="H267" t="n">
         <v>400</v>
@@ -8141,7 +8141,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G268" t="n">
-        <v>5.45264196395874</v>
+        <v>5.4526424407959</v>
       </c>
       <c r="H268" t="n">
         <v>8200</v>
@@ -8228,7 +8228,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G271" t="n">
-        <v>5.45264196395874</v>
+        <v>5.4526424407959</v>
       </c>
       <c r="H271" t="n">
         <v>800</v>
@@ -8257,7 +8257,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G272" t="n">
-        <v>5.45264196395874</v>
+        <v>5.4526424407959</v>
       </c>
       <c r="H272" t="n">
         <v>200</v>
@@ -8315,7 +8315,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G274" t="n">
-        <v>5.5500111579895</v>
+        <v>5.55001068115234</v>
       </c>
       <c r="H274" t="n">
         <v>3200</v>
@@ -25953,6 +25953,35 @@
         <v>1600</v>
       </c>
       <c r="I882" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="883">
+      <c r="A883" t="s">
+        <v>9</v>
+      </c>
+      <c r="B883" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C883" t="n">
+        <v>6.59999990463257</v>
+      </c>
+      <c r="D883" t="n">
+        <v>6.59999990463257</v>
+      </c>
+      <c r="E883" t="n">
+        <v>6.59999990463257</v>
+      </c>
+      <c r="F883" t="n">
+        <v>6.59999990463257</v>
+      </c>
+      <c r="G883" t="n">
+        <v>6.59999990463257</v>
+      </c>
+      <c r="H883" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I883" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ECMB.MI.xlsx
+++ b/data/ECMB.MI.xlsx
@@ -25985,6 +25985,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="884">
+      <c r="A884" t="s">
+        <v>9</v>
+      </c>
+      <c r="B884" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C884" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="D884" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E884" t="n">
+        <v>6.44999980926514</v>
+      </c>
+      <c r="F884" t="n">
+        <v>6.59999990463257</v>
+      </c>
+      <c r="G884" t="n">
+        <v>6.59999990463257</v>
+      </c>
+      <c r="H884" t="n">
+        <v>1800</v>
+      </c>
+      <c r="I884" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ECMB.MI.xlsx
+++ b/data/ECMB.MI.xlsx
@@ -485,7 +485,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G4" t="n">
-        <v>8.25685882568359</v>
+        <v>8.25685787200928</v>
       </c>
       <c r="H4" t="n">
         <v>7000</v>
@@ -514,7 +514,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G5" t="n">
-        <v>8.17896270751953</v>
+        <v>8.17896366119385</v>
       </c>
       <c r="H5" t="n">
         <v>1400</v>
@@ -572,7 +572,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G7" t="n">
-        <v>8.0815954208374</v>
+        <v>8.08159446716309</v>
       </c>
       <c r="H7" t="n">
         <v>4200</v>
@@ -630,7 +630,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G9" t="n">
-        <v>8.17896270751953</v>
+        <v>8.17896366119385</v>
       </c>
       <c r="H9" t="n">
         <v>200</v>
@@ -659,7 +659,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G10" t="n">
-        <v>8.17896270751953</v>
+        <v>8.17896366119385</v>
       </c>
       <c r="H10" t="n">
         <v>3600</v>
@@ -688,7 +688,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G11" t="n">
-        <v>8.14001655578613</v>
+        <v>8.14001560211182</v>
       </c>
       <c r="H11" t="n">
         <v>200</v>
@@ -804,7 +804,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G15" t="n">
-        <v>7.82843637466431</v>
+        <v>7.82843685150146</v>
       </c>
       <c r="H15" t="n">
         <v>2600</v>
@@ -833,7 +833,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G16" t="n">
-        <v>7.90633153915405</v>
+        <v>7.90633106231689</v>
       </c>
       <c r="H16" t="n">
         <v>6400</v>
@@ -891,7 +891,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G18" t="n">
-        <v>7.94527864456177</v>
+        <v>7.94527912139893</v>
       </c>
       <c r="H18" t="n">
         <v>2600</v>
@@ -920,7 +920,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G19" t="n">
-        <v>7.94527864456177</v>
+        <v>7.94527912139893</v>
       </c>
       <c r="H19" t="n">
         <v>600</v>
@@ -1036,7 +1036,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G23" t="n">
-        <v>7.77001523971558</v>
+        <v>7.77001571655273</v>
       </c>
       <c r="H23" t="n">
         <v>2600</v>
@@ -1152,7 +1152,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G27" t="n">
-        <v>7.94527864456177</v>
+        <v>7.94527912139893</v>
       </c>
       <c r="H27" t="n">
         <v>15200</v>
@@ -1181,7 +1181,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G28" t="n">
-        <v>7.94527864456177</v>
+        <v>7.94527912139893</v>
       </c>
       <c r="H28" t="n">
         <v>8200</v>
@@ -1210,7 +1210,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G29" t="n">
-        <v>7.77001523971558</v>
+        <v>7.77001571655273</v>
       </c>
       <c r="H29" t="n">
         <v>9000</v>
@@ -1239,7 +1239,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G30" t="n">
-        <v>7.77001523971558</v>
+        <v>7.77001571655273</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
@@ -1384,7 +1384,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G35" t="n">
-        <v>8.0815954208374</v>
+        <v>8.08159446716309</v>
       </c>
       <c r="H35" t="n">
         <v>1800</v>
@@ -1442,7 +1442,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G37" t="n">
-        <v>8.0815954208374</v>
+        <v>8.08159446716309</v>
       </c>
       <c r="H37" t="n">
         <v>3400</v>
@@ -1471,7 +1471,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G38" t="n">
-        <v>8.17896270751953</v>
+        <v>8.17896366119385</v>
       </c>
       <c r="H38" t="n">
         <v>14400</v>
@@ -1529,7 +1529,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G40" t="n">
-        <v>8.29580593109131</v>
+        <v>8.29580688476562</v>
       </c>
       <c r="H40" t="n">
         <v>4400</v>
@@ -1558,7 +1558,7 @@
         <v>8.5</v>
       </c>
       <c r="G41" t="n">
-        <v>8.27633190155029</v>
+        <v>8.27633285522461</v>
       </c>
       <c r="H41" t="n">
         <v>1200</v>
@@ -1587,7 +1587,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G42" t="n">
-        <v>8.17896270751953</v>
+        <v>8.17896366119385</v>
       </c>
       <c r="H42" t="n">
         <v>800</v>
@@ -1935,7 +1935,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G54" t="n">
-        <v>8.78264904022217</v>
+        <v>8.78264999389648</v>
       </c>
       <c r="H54" t="n">
         <v>4600</v>
@@ -1964,7 +1964,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G55" t="n">
-        <v>8.86054420471191</v>
+        <v>8.86054515838623</v>
       </c>
       <c r="H55" t="n">
         <v>6400</v>
@@ -2051,7 +2051,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G58" t="n">
-        <v>8.66580677032471</v>
+        <v>8.66580581665039</v>
       </c>
       <c r="H58" t="n">
         <v>2000</v>
@@ -2080,7 +2080,7 @@
         <v>8.92000007629395</v>
       </c>
       <c r="G59" t="n">
-        <v>8.68528079986572</v>
+        <v>8.68527984619141</v>
       </c>
       <c r="H59" t="n">
         <v>800</v>
@@ -2167,7 +2167,7 @@
         <v>8.5</v>
       </c>
       <c r="G62" t="n">
-        <v>8.27633190155029</v>
+        <v>8.27633285522461</v>
       </c>
       <c r="H62" t="n">
         <v>1600</v>
@@ -2196,7 +2196,7 @@
         <v>8.5</v>
       </c>
       <c r="G63" t="n">
-        <v>8.27633190155029</v>
+        <v>8.27633285522461</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
@@ -2283,7 +2283,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G66" t="n">
-        <v>8.0815954208374</v>
+        <v>8.08159446716309</v>
       </c>
       <c r="H66" t="n">
         <v>200</v>
@@ -2312,7 +2312,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G67" t="n">
-        <v>7.90633153915405</v>
+        <v>7.90633106231689</v>
       </c>
       <c r="H67" t="n">
         <v>3800</v>
@@ -2370,7 +2370,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G69" t="n">
-        <v>7.94527864456177</v>
+        <v>7.94527912139893</v>
       </c>
       <c r="H69" t="n">
         <v>2800</v>
@@ -2457,7 +2457,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G72" t="n">
-        <v>7.94527864456177</v>
+        <v>7.94527912139893</v>
       </c>
       <c r="H72" t="n">
         <v>1000</v>
@@ -2544,7 +2544,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G75" t="n">
-        <v>8.0815954208374</v>
+        <v>8.08159446716309</v>
       </c>
       <c r="H75" t="n">
         <v>2600</v>
@@ -2573,7 +2573,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G76" t="n">
-        <v>7.75054216384888</v>
+        <v>7.75054168701172</v>
       </c>
       <c r="H76" t="n">
         <v>4200</v>
@@ -2660,7 +2660,7 @@
         <v>7.76000022888184</v>
       </c>
       <c r="G79" t="n">
-        <v>7.55580472946167</v>
+        <v>7.55580520629883</v>
       </c>
       <c r="H79" t="n">
         <v>200</v>
@@ -2718,7 +2718,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G81" t="n">
-        <v>7.65317296981812</v>
+        <v>7.65317344665527</v>
       </c>
       <c r="H81" t="n">
         <v>400</v>
@@ -2747,7 +2747,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G82" t="n">
-        <v>7.65317296981812</v>
+        <v>7.65317344665527</v>
       </c>
       <c r="H82" t="n">
         <v>0</v>
@@ -2834,7 +2834,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G85" t="n">
-        <v>7.82843637466431</v>
+        <v>7.82843685150146</v>
       </c>
       <c r="H85" t="n">
         <v>200</v>
@@ -2863,7 +2863,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G86" t="n">
-        <v>7.82843637466431</v>
+        <v>7.82843685150146</v>
       </c>
       <c r="H86" t="n">
         <v>200</v>
@@ -2892,7 +2892,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G87" t="n">
-        <v>7.80896377563477</v>
+        <v>7.80896329879761</v>
       </c>
       <c r="H87" t="n">
         <v>2000</v>
@@ -2921,7 +2921,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G88" t="n">
-        <v>7.82843637466431</v>
+        <v>7.82843685150146</v>
       </c>
       <c r="H88" t="n">
         <v>2400</v>
@@ -3008,7 +3008,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G91" t="n">
-        <v>7.63369989395142</v>
+        <v>7.63369941711426</v>
       </c>
       <c r="H91" t="n">
         <v>800</v>
@@ -3124,7 +3124,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G95" t="n">
-        <v>7.80896377563477</v>
+        <v>7.80896329879761</v>
       </c>
       <c r="H95" t="n">
         <v>200</v>
@@ -3153,7 +3153,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G96" t="n">
-        <v>7.80896377563477</v>
+        <v>7.80896329879761</v>
       </c>
       <c r="H96" t="n">
         <v>0</v>
@@ -3298,7 +3298,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G101" t="n">
-        <v>7.84791088104248</v>
+        <v>7.84791040420532</v>
       </c>
       <c r="H101" t="n">
         <v>200</v>
@@ -3414,7 +3414,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G105" t="n">
-        <v>7.94527864456177</v>
+        <v>7.94527912139893</v>
       </c>
       <c r="H105" t="n">
         <v>1000</v>
@@ -3559,7 +3559,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G110" t="n">
-        <v>7.47790908813477</v>
+        <v>7.47790956497192</v>
       </c>
       <c r="H110" t="n">
         <v>1600</v>
@@ -3588,7 +3588,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G111" t="n">
-        <v>7.47790908813477</v>
+        <v>7.47790956497192</v>
       </c>
       <c r="H111" t="n">
         <v>0</v>
@@ -3820,7 +3820,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G119" t="n">
-        <v>8.0815954208374</v>
+        <v>8.08159446716309</v>
       </c>
       <c r="H119" t="n">
         <v>400</v>
@@ -3849,7 +3849,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G120" t="n">
-        <v>8.0815954208374</v>
+        <v>8.08159446716309</v>
       </c>
       <c r="H120" t="n">
         <v>0</v>
@@ -3878,7 +3878,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G121" t="n">
-        <v>7.90633153915405</v>
+        <v>7.90633106231689</v>
       </c>
       <c r="H121" t="n">
         <v>600</v>
@@ -3907,7 +3907,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G122" t="n">
-        <v>7.90633153915405</v>
+        <v>7.90633106231689</v>
       </c>
       <c r="H122" t="n">
         <v>0</v>
@@ -3965,7 +3965,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G124" t="n">
-        <v>8.04264736175537</v>
+        <v>8.04264831542969</v>
       </c>
       <c r="H124" t="n">
         <v>1600</v>
@@ -4110,7 +4110,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G129" t="n">
-        <v>7.82843637466431</v>
+        <v>7.82843685150146</v>
       </c>
       <c r="H129" t="n">
         <v>200</v>
@@ -4139,7 +4139,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G130" t="n">
-        <v>7.82843637466431</v>
+        <v>7.82843685150146</v>
       </c>
       <c r="H130" t="n">
         <v>0</v>
@@ -4255,7 +4255,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G134" t="n">
-        <v>7.75054216384888</v>
+        <v>7.75054168701172</v>
       </c>
       <c r="H134" t="n">
         <v>200</v>
@@ -4284,7 +4284,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G135" t="n">
-        <v>7.94527864456177</v>
+        <v>7.94527912139893</v>
       </c>
       <c r="H135" t="n">
         <v>800</v>
@@ -4313,7 +4313,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G136" t="n">
-        <v>7.94527864456177</v>
+        <v>7.94527912139893</v>
       </c>
       <c r="H136" t="n">
         <v>0</v>
@@ -4458,7 +4458,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G141" t="n">
-        <v>7.82843637466431</v>
+        <v>7.82843685150146</v>
       </c>
       <c r="H141" t="n">
         <v>600</v>
@@ -4487,7 +4487,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G142" t="n">
-        <v>7.82843637466431</v>
+        <v>7.82843685150146</v>
       </c>
       <c r="H142" t="n">
         <v>0</v>
@@ -4835,7 +4835,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G154" t="n">
-        <v>7.45843601226807</v>
+        <v>7.45843553543091</v>
       </c>
       <c r="H154" t="n">
         <v>400</v>
@@ -4922,7 +4922,7 @@
         <v>7.78000020980835</v>
       </c>
       <c r="G157" t="n">
-        <v>7.57527875900269</v>
+        <v>7.57527828216553</v>
       </c>
       <c r="H157" t="n">
         <v>600</v>
@@ -5241,7 +5241,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G168" t="n">
-        <v>6.42632818222046</v>
+        <v>6.42632865905762</v>
       </c>
       <c r="H168" t="n">
         <v>15400</v>
@@ -5531,7 +5531,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G178" t="n">
-        <v>7.08843517303467</v>
+        <v>7.08843564987183</v>
       </c>
       <c r="H178" t="n">
         <v>1000</v>
@@ -5560,7 +5560,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G179" t="n">
-        <v>7.08843517303467</v>
+        <v>7.08843564987183</v>
       </c>
       <c r="H179" t="n">
         <v>200</v>
@@ -5589,7 +5589,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G180" t="n">
-        <v>6.83527660369873</v>
+        <v>6.83527708053589</v>
       </c>
       <c r="H180" t="n">
         <v>4400</v>
@@ -5647,7 +5647,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G182" t="n">
-        <v>6.73790836334229</v>
+        <v>6.73790788650513</v>
       </c>
       <c r="H182" t="n">
         <v>800</v>
@@ -6082,7 +6082,7 @@
         <v>7.78000020980835</v>
       </c>
       <c r="G197" t="n">
-        <v>7.57527875900269</v>
+        <v>7.57527828216553</v>
       </c>
       <c r="H197" t="n">
         <v>3000</v>
@@ -6140,7 +6140,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G199" t="n">
-        <v>7.28317260742188</v>
+        <v>7.28317213058472</v>
       </c>
       <c r="H199" t="n">
         <v>2200</v>
@@ -6169,7 +6169,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G200" t="n">
-        <v>7.12738275527954</v>
+        <v>7.1273832321167</v>
       </c>
       <c r="H200" t="n">
         <v>3000</v>
@@ -6227,7 +6227,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G202" t="n">
-        <v>6.54317045211792</v>
+        <v>6.54317092895508</v>
       </c>
       <c r="H202" t="n">
         <v>1600</v>
@@ -6256,7 +6256,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G203" t="n">
-        <v>6.54317045211792</v>
+        <v>6.54317092895508</v>
       </c>
       <c r="H203" t="n">
         <v>3000</v>
@@ -6285,7 +6285,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G204" t="n">
-        <v>6.54317045211792</v>
+        <v>6.54317092895508</v>
       </c>
       <c r="H204" t="n">
         <v>0</v>
@@ -6343,7 +6343,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G206" t="n">
-        <v>6.27053880691528</v>
+        <v>6.27053928375244</v>
       </c>
       <c r="H206" t="n">
         <v>10600</v>
@@ -6372,7 +6372,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G207" t="n">
-        <v>6.2900128364563</v>
+        <v>6.29001235961914</v>
       </c>
       <c r="H207" t="n">
         <v>2200</v>
@@ -6459,7 +6459,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G210" t="n">
-        <v>6.42632818222046</v>
+        <v>6.42632865905762</v>
       </c>
       <c r="H210" t="n">
         <v>4200</v>
@@ -6575,7 +6575,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G214" t="n">
-        <v>5.97843265533447</v>
+        <v>5.97843313217163</v>
       </c>
       <c r="H214" t="n">
         <v>7800</v>
@@ -6604,7 +6604,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G215" t="n">
-        <v>5.9200119972229</v>
+        <v>5.92001152038574</v>
       </c>
       <c r="H215" t="n">
         <v>10000</v>
@@ -6633,7 +6633,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G216" t="n">
-        <v>5.9200119972229</v>
+        <v>5.92001152038574</v>
       </c>
       <c r="H216" t="n">
         <v>8200</v>
@@ -6952,7 +6952,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G227" t="n">
-        <v>5.74474859237671</v>
+        <v>5.74474811553955</v>
       </c>
       <c r="H227" t="n">
         <v>200</v>
@@ -7010,7 +7010,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G229" t="n">
-        <v>5.62790632247925</v>
+        <v>5.62790584564209</v>
       </c>
       <c r="H229" t="n">
         <v>11400</v>
@@ -7097,7 +7097,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G232" t="n">
-        <v>5.74474859237671</v>
+        <v>5.74474811553955</v>
       </c>
       <c r="H232" t="n">
         <v>200</v>
@@ -7126,7 +7126,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G233" t="n">
-        <v>5.74474859237671</v>
+        <v>5.74474811553955</v>
       </c>
       <c r="H233" t="n">
         <v>5800</v>
@@ -7184,7 +7184,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G235" t="n">
-        <v>5.74474859237671</v>
+        <v>5.74474811553955</v>
       </c>
       <c r="H235" t="n">
         <v>600</v>
@@ -7213,7 +7213,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G236" t="n">
-        <v>5.74474859237671</v>
+        <v>5.74474811553955</v>
       </c>
       <c r="H236" t="n">
         <v>0</v>
@@ -7590,7 +7590,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G249" t="n">
-        <v>5.74474859237671</v>
+        <v>5.74474811553955</v>
       </c>
       <c r="H249" t="n">
         <v>400</v>
@@ -7648,7 +7648,7 @@
         <v>5.5</v>
       </c>
       <c r="G251" t="n">
-        <v>5.35527420043945</v>
+        <v>5.35527372360229</v>
       </c>
       <c r="H251" t="n">
         <v>3400</v>
@@ -7706,7 +7706,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G253" t="n">
-        <v>5.06316804885864</v>
+        <v>5.06316757202148</v>
       </c>
       <c r="H253" t="n">
         <v>4000</v>
@@ -7880,7 +7880,7 @@
         <v>5.5</v>
       </c>
       <c r="G259" t="n">
-        <v>5.35527420043945</v>
+        <v>5.35527372360229</v>
       </c>
       <c r="H259" t="n">
         <v>200</v>
@@ -7909,7 +7909,7 @@
         <v>5.25</v>
       </c>
       <c r="G260" t="n">
-        <v>5.11185264587402</v>
+        <v>5.11185216903687</v>
       </c>
       <c r="H260" t="n">
         <v>16800</v>
@@ -7938,7 +7938,7 @@
         <v>5</v>
       </c>
       <c r="G261" t="n">
-        <v>4.86843061447144</v>
+        <v>4.86843109130859</v>
       </c>
       <c r="H261" t="n">
         <v>10600</v>
@@ -7967,7 +7967,7 @@
         <v>5</v>
       </c>
       <c r="G262" t="n">
-        <v>4.86843061447144</v>
+        <v>4.86843109130859</v>
       </c>
       <c r="H262" t="n">
         <v>15600</v>
@@ -7996,7 +7996,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G263" t="n">
-        <v>5.25790500640869</v>
+        <v>5.25790548324585</v>
       </c>
       <c r="H263" t="n">
         <v>35800</v>
@@ -8054,7 +8054,7 @@
         <v>5.25</v>
       </c>
       <c r="G265" t="n">
-        <v>5.11185264587402</v>
+        <v>5.11185216903687</v>
       </c>
       <c r="H265" t="n">
         <v>77400</v>
@@ -8112,7 +8112,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G267" t="n">
-        <v>5.25790500640869</v>
+        <v>5.25790548324585</v>
       </c>
       <c r="H267" t="n">
         <v>400</v>
@@ -8141,7 +8141,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G268" t="n">
-        <v>5.4526424407959</v>
+        <v>5.45264196395874</v>
       </c>
       <c r="H268" t="n">
         <v>8200</v>
@@ -8228,7 +8228,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G271" t="n">
-        <v>5.4526424407959</v>
+        <v>5.45264196395874</v>
       </c>
       <c r="H271" t="n">
         <v>800</v>
@@ -8257,7 +8257,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G272" t="n">
-        <v>5.4526424407959</v>
+        <v>5.45264196395874</v>
       </c>
       <c r="H272" t="n">
         <v>200</v>
@@ -8315,7 +8315,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G274" t="n">
-        <v>5.55001068115234</v>
+        <v>5.5500111579895</v>
       </c>
       <c r="H274" t="n">
         <v>3200</v>
@@ -25996,7 +25996,7 @@
         <v>6.5</v>
       </c>
       <c r="D884" t="n">
-        <v>6.5</v>
+        <v>6.59999990463257</v>
       </c>
       <c r="E884" t="n">
         <v>6.44999980926514</v>
@@ -26011,6 +26011,35 @@
         <v>1800</v>
       </c>
       <c r="I884" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="885">
+      <c r="A885" t="s">
+        <v>9</v>
+      </c>
+      <c r="B885" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C885" t="n">
+        <v>6.44999980926514</v>
+      </c>
+      <c r="D885" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E885" t="n">
+        <v>6.44999980926514</v>
+      </c>
+      <c r="F885" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G885" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H885" t="n">
+        <v>400</v>
+      </c>
+      <c r="I885" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ECMB.MI.xlsx
+++ b/data/ECMB.MI.xlsx
@@ -485,7 +485,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G4" t="n">
-        <v>8.25685787200928</v>
+        <v>8.25685882568359</v>
       </c>
       <c r="H4" t="n">
         <v>7000</v>
@@ -514,7 +514,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G5" t="n">
-        <v>8.17896366119385</v>
+        <v>8.17896270751953</v>
       </c>
       <c r="H5" t="n">
         <v>1400</v>
@@ -572,7 +572,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G7" t="n">
-        <v>8.08159446716309</v>
+        <v>8.0815954208374</v>
       </c>
       <c r="H7" t="n">
         <v>4200</v>
@@ -630,7 +630,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G9" t="n">
-        <v>8.17896366119385</v>
+        <v>8.17896270751953</v>
       </c>
       <c r="H9" t="n">
         <v>200</v>
@@ -659,7 +659,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G10" t="n">
-        <v>8.17896366119385</v>
+        <v>8.17896270751953</v>
       </c>
       <c r="H10" t="n">
         <v>3600</v>
@@ -688,7 +688,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G11" t="n">
-        <v>8.14001560211182</v>
+        <v>8.14001655578613</v>
       </c>
       <c r="H11" t="n">
         <v>200</v>
@@ -804,7 +804,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G15" t="n">
-        <v>7.82843685150146</v>
+        <v>7.82843637466431</v>
       </c>
       <c r="H15" t="n">
         <v>2600</v>
@@ -833,7 +833,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G16" t="n">
-        <v>7.90633106231689</v>
+        <v>7.90633153915405</v>
       </c>
       <c r="H16" t="n">
         <v>6400</v>
@@ -891,7 +891,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G18" t="n">
-        <v>7.94527912139893</v>
+        <v>7.94527864456177</v>
       </c>
       <c r="H18" t="n">
         <v>2600</v>
@@ -920,7 +920,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G19" t="n">
-        <v>7.94527912139893</v>
+        <v>7.94527864456177</v>
       </c>
       <c r="H19" t="n">
         <v>600</v>
@@ -1036,7 +1036,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G23" t="n">
-        <v>7.77001571655273</v>
+        <v>7.77001523971558</v>
       </c>
       <c r="H23" t="n">
         <v>2600</v>
@@ -1152,7 +1152,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G27" t="n">
-        <v>7.94527912139893</v>
+        <v>7.94527864456177</v>
       </c>
       <c r="H27" t="n">
         <v>15200</v>
@@ -1181,7 +1181,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G28" t="n">
-        <v>7.94527912139893</v>
+        <v>7.94527864456177</v>
       </c>
       <c r="H28" t="n">
         <v>8200</v>
@@ -1210,7 +1210,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G29" t="n">
-        <v>7.77001571655273</v>
+        <v>7.77001523971558</v>
       </c>
       <c r="H29" t="n">
         <v>9000</v>
@@ -1239,7 +1239,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G30" t="n">
-        <v>7.77001571655273</v>
+        <v>7.77001523971558</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
@@ -1384,7 +1384,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G35" t="n">
-        <v>8.08159446716309</v>
+        <v>8.0815954208374</v>
       </c>
       <c r="H35" t="n">
         <v>1800</v>
@@ -1442,7 +1442,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G37" t="n">
-        <v>8.08159446716309</v>
+        <v>8.0815954208374</v>
       </c>
       <c r="H37" t="n">
         <v>3400</v>
@@ -1471,7 +1471,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G38" t="n">
-        <v>8.17896366119385</v>
+        <v>8.17896270751953</v>
       </c>
       <c r="H38" t="n">
         <v>14400</v>
@@ -1529,7 +1529,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G40" t="n">
-        <v>8.29580688476562</v>
+        <v>8.29580593109131</v>
       </c>
       <c r="H40" t="n">
         <v>4400</v>
@@ -1558,7 +1558,7 @@
         <v>8.5</v>
       </c>
       <c r="G41" t="n">
-        <v>8.27633285522461</v>
+        <v>8.27633190155029</v>
       </c>
       <c r="H41" t="n">
         <v>1200</v>
@@ -1587,7 +1587,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G42" t="n">
-        <v>8.17896366119385</v>
+        <v>8.17896270751953</v>
       </c>
       <c r="H42" t="n">
         <v>800</v>
@@ -1935,7 +1935,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G54" t="n">
-        <v>8.78264999389648</v>
+        <v>8.78264904022217</v>
       </c>
       <c r="H54" t="n">
         <v>4600</v>
@@ -1964,7 +1964,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G55" t="n">
-        <v>8.86054515838623</v>
+        <v>8.86054420471191</v>
       </c>
       <c r="H55" t="n">
         <v>6400</v>
@@ -2051,7 +2051,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G58" t="n">
-        <v>8.66580581665039</v>
+        <v>8.66580677032471</v>
       </c>
       <c r="H58" t="n">
         <v>2000</v>
@@ -2080,7 +2080,7 @@
         <v>8.92000007629395</v>
       </c>
       <c r="G59" t="n">
-        <v>8.68527984619141</v>
+        <v>8.68528079986572</v>
       </c>
       <c r="H59" t="n">
         <v>800</v>
@@ -2167,7 +2167,7 @@
         <v>8.5</v>
       </c>
       <c r="G62" t="n">
-        <v>8.27633285522461</v>
+        <v>8.27633190155029</v>
       </c>
       <c r="H62" t="n">
         <v>1600</v>
@@ -2196,7 +2196,7 @@
         <v>8.5</v>
       </c>
       <c r="G63" t="n">
-        <v>8.27633285522461</v>
+        <v>8.27633190155029</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
@@ -2283,7 +2283,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G66" t="n">
-        <v>8.08159446716309</v>
+        <v>8.0815954208374</v>
       </c>
       <c r="H66" t="n">
         <v>200</v>
@@ -2312,7 +2312,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G67" t="n">
-        <v>7.90633106231689</v>
+        <v>7.90633153915405</v>
       </c>
       <c r="H67" t="n">
         <v>3800</v>
@@ -2370,7 +2370,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G69" t="n">
-        <v>7.94527912139893</v>
+        <v>7.94527864456177</v>
       </c>
       <c r="H69" t="n">
         <v>2800</v>
@@ -2457,7 +2457,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G72" t="n">
-        <v>7.94527912139893</v>
+        <v>7.94527864456177</v>
       </c>
       <c r="H72" t="n">
         <v>1000</v>
@@ -2544,7 +2544,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G75" t="n">
-        <v>8.08159446716309</v>
+        <v>8.0815954208374</v>
       </c>
       <c r="H75" t="n">
         <v>2600</v>
@@ -2573,7 +2573,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G76" t="n">
-        <v>7.75054168701172</v>
+        <v>7.75054216384888</v>
       </c>
       <c r="H76" t="n">
         <v>4200</v>
@@ -2660,7 +2660,7 @@
         <v>7.76000022888184</v>
       </c>
       <c r="G79" t="n">
-        <v>7.55580520629883</v>
+        <v>7.55580472946167</v>
       </c>
       <c r="H79" t="n">
         <v>200</v>
@@ -2718,7 +2718,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G81" t="n">
-        <v>7.65317344665527</v>
+        <v>7.65317296981812</v>
       </c>
       <c r="H81" t="n">
         <v>400</v>
@@ -2747,7 +2747,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G82" t="n">
-        <v>7.65317344665527</v>
+        <v>7.65317296981812</v>
       </c>
       <c r="H82" t="n">
         <v>0</v>
@@ -2834,7 +2834,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G85" t="n">
-        <v>7.82843685150146</v>
+        <v>7.82843637466431</v>
       </c>
       <c r="H85" t="n">
         <v>200</v>
@@ -2863,7 +2863,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G86" t="n">
-        <v>7.82843685150146</v>
+        <v>7.82843637466431</v>
       </c>
       <c r="H86" t="n">
         <v>200</v>
@@ -2892,7 +2892,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G87" t="n">
-        <v>7.80896329879761</v>
+        <v>7.80896377563477</v>
       </c>
       <c r="H87" t="n">
         <v>2000</v>
@@ -2921,7 +2921,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G88" t="n">
-        <v>7.82843685150146</v>
+        <v>7.82843637466431</v>
       </c>
       <c r="H88" t="n">
         <v>2400</v>
@@ -3008,7 +3008,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G91" t="n">
-        <v>7.63369941711426</v>
+        <v>7.63369989395142</v>
       </c>
       <c r="H91" t="n">
         <v>800</v>
@@ -3124,7 +3124,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G95" t="n">
-        <v>7.80896329879761</v>
+        <v>7.80896377563477</v>
       </c>
       <c r="H95" t="n">
         <v>200</v>
@@ -3153,7 +3153,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G96" t="n">
-        <v>7.80896329879761</v>
+        <v>7.80896377563477</v>
       </c>
       <c r="H96" t="n">
         <v>0</v>
@@ -3298,7 +3298,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G101" t="n">
-        <v>7.84791040420532</v>
+        <v>7.84791088104248</v>
       </c>
       <c r="H101" t="n">
         <v>200</v>
@@ -3414,7 +3414,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G105" t="n">
-        <v>7.94527912139893</v>
+        <v>7.94527864456177</v>
       </c>
       <c r="H105" t="n">
         <v>1000</v>
@@ -3559,7 +3559,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G110" t="n">
-        <v>7.47790956497192</v>
+        <v>7.47790908813477</v>
       </c>
       <c r="H110" t="n">
         <v>1600</v>
@@ -3588,7 +3588,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G111" t="n">
-        <v>7.47790956497192</v>
+        <v>7.47790908813477</v>
       </c>
       <c r="H111" t="n">
         <v>0</v>
@@ -3820,7 +3820,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G119" t="n">
-        <v>8.08159446716309</v>
+        <v>8.0815954208374</v>
       </c>
       <c r="H119" t="n">
         <v>400</v>
@@ -3849,7 +3849,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G120" t="n">
-        <v>8.08159446716309</v>
+        <v>8.0815954208374</v>
       </c>
       <c r="H120" t="n">
         <v>0</v>
@@ -3878,7 +3878,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G121" t="n">
-        <v>7.90633106231689</v>
+        <v>7.90633153915405</v>
       </c>
       <c r="H121" t="n">
         <v>600</v>
@@ -3907,7 +3907,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G122" t="n">
-        <v>7.90633106231689</v>
+        <v>7.90633153915405</v>
       </c>
       <c r="H122" t="n">
         <v>0</v>
@@ -3965,7 +3965,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G124" t="n">
-        <v>8.04264831542969</v>
+        <v>8.04264736175537</v>
       </c>
       <c r="H124" t="n">
         <v>1600</v>
@@ -4110,7 +4110,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G129" t="n">
-        <v>7.82843685150146</v>
+        <v>7.82843637466431</v>
       </c>
       <c r="H129" t="n">
         <v>200</v>
@@ -4139,7 +4139,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G130" t="n">
-        <v>7.82843685150146</v>
+        <v>7.82843637466431</v>
       </c>
       <c r="H130" t="n">
         <v>0</v>
@@ -4255,7 +4255,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G134" t="n">
-        <v>7.75054168701172</v>
+        <v>7.75054216384888</v>
       </c>
       <c r="H134" t="n">
         <v>200</v>
@@ -4284,7 +4284,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G135" t="n">
-        <v>7.94527912139893</v>
+        <v>7.94527864456177</v>
       </c>
       <c r="H135" t="n">
         <v>800</v>
@@ -4313,7 +4313,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G136" t="n">
-        <v>7.94527912139893</v>
+        <v>7.94527864456177</v>
       </c>
       <c r="H136" t="n">
         <v>0</v>
@@ -4458,7 +4458,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G141" t="n">
-        <v>7.82843685150146</v>
+        <v>7.82843637466431</v>
       </c>
       <c r="H141" t="n">
         <v>600</v>
@@ -4487,7 +4487,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G142" t="n">
-        <v>7.82843685150146</v>
+        <v>7.82843637466431</v>
       </c>
       <c r="H142" t="n">
         <v>0</v>
@@ -4835,7 +4835,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G154" t="n">
-        <v>7.45843553543091</v>
+        <v>7.45843601226807</v>
       </c>
       <c r="H154" t="n">
         <v>400</v>
@@ -4922,7 +4922,7 @@
         <v>7.78000020980835</v>
       </c>
       <c r="G157" t="n">
-        <v>7.57527828216553</v>
+        <v>7.57527875900269</v>
       </c>
       <c r="H157" t="n">
         <v>600</v>
@@ -5241,7 +5241,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G168" t="n">
-        <v>6.42632865905762</v>
+        <v>6.42632818222046</v>
       </c>
       <c r="H168" t="n">
         <v>15400</v>
@@ -5531,7 +5531,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G178" t="n">
-        <v>7.08843564987183</v>
+        <v>7.08843517303467</v>
       </c>
       <c r="H178" t="n">
         <v>1000</v>
@@ -5560,7 +5560,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G179" t="n">
-        <v>7.08843564987183</v>
+        <v>7.08843517303467</v>
       </c>
       <c r="H179" t="n">
         <v>200</v>
@@ -5589,7 +5589,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G180" t="n">
-        <v>6.83527708053589</v>
+        <v>6.83527660369873</v>
       </c>
       <c r="H180" t="n">
         <v>4400</v>
@@ -5647,7 +5647,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G182" t="n">
-        <v>6.73790788650513</v>
+        <v>6.73790836334229</v>
       </c>
       <c r="H182" t="n">
         <v>800</v>
@@ -6082,7 +6082,7 @@
         <v>7.78000020980835</v>
       </c>
       <c r="G197" t="n">
-        <v>7.57527828216553</v>
+        <v>7.57527875900269</v>
       </c>
       <c r="H197" t="n">
         <v>3000</v>
@@ -6140,7 +6140,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G199" t="n">
-        <v>7.28317213058472</v>
+        <v>7.28317260742188</v>
       </c>
       <c r="H199" t="n">
         <v>2200</v>
@@ -6169,7 +6169,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G200" t="n">
-        <v>7.1273832321167</v>
+        <v>7.12738275527954</v>
       </c>
       <c r="H200" t="n">
         <v>3000</v>
@@ -6227,7 +6227,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G202" t="n">
-        <v>6.54317092895508</v>
+        <v>6.54317045211792</v>
       </c>
       <c r="H202" t="n">
         <v>1600</v>
@@ -6256,7 +6256,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G203" t="n">
-        <v>6.54317092895508</v>
+        <v>6.54317045211792</v>
       </c>
       <c r="H203" t="n">
         <v>3000</v>
@@ -6285,7 +6285,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G204" t="n">
-        <v>6.54317092895508</v>
+        <v>6.54317045211792</v>
       </c>
       <c r="H204" t="n">
         <v>0</v>
@@ -6343,7 +6343,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G206" t="n">
-        <v>6.27053928375244</v>
+        <v>6.27053880691528</v>
       </c>
       <c r="H206" t="n">
         <v>10600</v>
@@ -6372,7 +6372,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G207" t="n">
-        <v>6.29001235961914</v>
+        <v>6.2900128364563</v>
       </c>
       <c r="H207" t="n">
         <v>2200</v>
@@ -6459,7 +6459,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G210" t="n">
-        <v>6.42632865905762</v>
+        <v>6.42632818222046</v>
       </c>
       <c r="H210" t="n">
         <v>4200</v>
@@ -6575,7 +6575,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G214" t="n">
-        <v>5.97843313217163</v>
+        <v>5.97843265533447</v>
       </c>
       <c r="H214" t="n">
         <v>7800</v>
@@ -6604,7 +6604,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G215" t="n">
-        <v>5.92001152038574</v>
+        <v>5.9200119972229</v>
       </c>
       <c r="H215" t="n">
         <v>10000</v>
@@ -6633,7 +6633,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G216" t="n">
-        <v>5.92001152038574</v>
+        <v>5.9200119972229</v>
       </c>
       <c r="H216" t="n">
         <v>8200</v>
@@ -6952,7 +6952,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G227" t="n">
-        <v>5.74474811553955</v>
+        <v>5.74474859237671</v>
       </c>
       <c r="H227" t="n">
         <v>200</v>
@@ -7010,7 +7010,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G229" t="n">
-        <v>5.62790584564209</v>
+        <v>5.62790632247925</v>
       </c>
       <c r="H229" t="n">
         <v>11400</v>
@@ -7097,7 +7097,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G232" t="n">
-        <v>5.74474811553955</v>
+        <v>5.74474859237671</v>
       </c>
       <c r="H232" t="n">
         <v>200</v>
@@ -7126,7 +7126,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G233" t="n">
-        <v>5.74474811553955</v>
+        <v>5.74474859237671</v>
       </c>
       <c r="H233" t="n">
         <v>5800</v>
@@ -7184,7 +7184,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G235" t="n">
-        <v>5.74474811553955</v>
+        <v>5.74474859237671</v>
       </c>
       <c r="H235" t="n">
         <v>600</v>
@@ -7213,7 +7213,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G236" t="n">
-        <v>5.74474811553955</v>
+        <v>5.74474859237671</v>
       </c>
       <c r="H236" t="n">
         <v>0</v>
@@ -7590,7 +7590,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G249" t="n">
-        <v>5.74474811553955</v>
+        <v>5.74474859237671</v>
       </c>
       <c r="H249" t="n">
         <v>400</v>
@@ -7648,7 +7648,7 @@
         <v>5.5</v>
       </c>
       <c r="G251" t="n">
-        <v>5.35527372360229</v>
+        <v>5.35527420043945</v>
       </c>
       <c r="H251" t="n">
         <v>3400</v>
@@ -7706,7 +7706,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G253" t="n">
-        <v>5.06316757202148</v>
+        <v>5.06316804885864</v>
       </c>
       <c r="H253" t="n">
         <v>4000</v>
@@ -7880,7 +7880,7 @@
         <v>5.5</v>
       </c>
       <c r="G259" t="n">
-        <v>5.35527372360229</v>
+        <v>5.35527420043945</v>
       </c>
       <c r="H259" t="n">
         <v>200</v>
@@ -7909,7 +7909,7 @@
         <v>5.25</v>
       </c>
       <c r="G260" t="n">
-        <v>5.11185216903687</v>
+        <v>5.11185264587402</v>
       </c>
       <c r="H260" t="n">
         <v>16800</v>
@@ -7938,7 +7938,7 @@
         <v>5</v>
       </c>
       <c r="G261" t="n">
-        <v>4.86843109130859</v>
+        <v>4.86843061447144</v>
       </c>
       <c r="H261" t="n">
         <v>10600</v>
@@ -7967,7 +7967,7 @@
         <v>5</v>
       </c>
       <c r="G262" t="n">
-        <v>4.86843109130859</v>
+        <v>4.86843061447144</v>
       </c>
       <c r="H262" t="n">
         <v>15600</v>
@@ -7996,7 +7996,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G263" t="n">
-        <v>5.25790548324585</v>
+        <v>5.25790500640869</v>
       </c>
       <c r="H263" t="n">
         <v>35800</v>
@@ -8054,7 +8054,7 @@
         <v>5.25</v>
       </c>
       <c r="G265" t="n">
-        <v>5.11185216903687</v>
+        <v>5.11185264587402</v>
       </c>
       <c r="H265" t="n">
         <v>77400</v>
@@ -8112,7 +8112,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G267" t="n">
-        <v>5.25790548324585</v>
+        <v>5.25790500640869</v>
       </c>
       <c r="H267" t="n">
         <v>400</v>
@@ -8141,7 +8141,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G268" t="n">
-        <v>5.45264196395874</v>
+        <v>5.4526424407959</v>
       </c>
       <c r="H268" t="n">
         <v>8200</v>
@@ -8228,7 +8228,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G271" t="n">
-        <v>5.45264196395874</v>
+        <v>5.4526424407959</v>
       </c>
       <c r="H271" t="n">
         <v>800</v>
@@ -8257,7 +8257,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G272" t="n">
-        <v>5.45264196395874</v>
+        <v>5.4526424407959</v>
       </c>
       <c r="H272" t="n">
         <v>200</v>
@@ -8315,7 +8315,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G274" t="n">
-        <v>5.5500111579895</v>
+        <v>5.55001068115234</v>
       </c>
       <c r="H274" t="n">
         <v>3200</v>
@@ -26040,6 +26040,35 @@
         <v>400</v>
       </c>
       <c r="I885" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="886">
+      <c r="A886" t="s">
+        <v>9</v>
+      </c>
+      <c r="B886" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C886" t="n">
+        <v>6.40000009536743</v>
+      </c>
+      <c r="D886" t="n">
+        <v>6.40000009536743</v>
+      </c>
+      <c r="E886" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="F886" t="n">
+        <v>6.30000019073486</v>
+      </c>
+      <c r="G886" t="n">
+        <v>6.30000019073486</v>
+      </c>
+      <c r="H886" t="n">
+        <v>2200</v>
+      </c>
+      <c r="I886" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ECMB.MI.xlsx
+++ b/data/ECMB.MI.xlsx
@@ -485,7 +485,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G4" t="n">
-        <v>8.25685882568359</v>
+        <v>8.25685787200928</v>
       </c>
       <c r="H4" t="n">
         <v>7000</v>
@@ -514,7 +514,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G5" t="n">
-        <v>8.17896270751953</v>
+        <v>8.17896366119385</v>
       </c>
       <c r="H5" t="n">
         <v>1400</v>
@@ -572,7 +572,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G7" t="n">
-        <v>8.0815954208374</v>
+        <v>8.08159446716309</v>
       </c>
       <c r="H7" t="n">
         <v>4200</v>
@@ -630,7 +630,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G9" t="n">
-        <v>8.17896270751953</v>
+        <v>8.17896366119385</v>
       </c>
       <c r="H9" t="n">
         <v>200</v>
@@ -659,7 +659,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G10" t="n">
-        <v>8.17896270751953</v>
+        <v>8.17896366119385</v>
       </c>
       <c r="H10" t="n">
         <v>3600</v>
@@ -688,7 +688,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G11" t="n">
-        <v>8.14001655578613</v>
+        <v>8.14001560211182</v>
       </c>
       <c r="H11" t="n">
         <v>200</v>
@@ -804,7 +804,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G15" t="n">
-        <v>7.82843637466431</v>
+        <v>7.82843685150146</v>
       </c>
       <c r="H15" t="n">
         <v>2600</v>
@@ -833,7 +833,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G16" t="n">
-        <v>7.90633153915405</v>
+        <v>7.90633106231689</v>
       </c>
       <c r="H16" t="n">
         <v>6400</v>
@@ -891,7 +891,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G18" t="n">
-        <v>7.94527864456177</v>
+        <v>7.94527912139893</v>
       </c>
       <c r="H18" t="n">
         <v>2600</v>
@@ -920,7 +920,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G19" t="n">
-        <v>7.94527864456177</v>
+        <v>7.94527912139893</v>
       </c>
       <c r="H19" t="n">
         <v>600</v>
@@ -1036,7 +1036,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G23" t="n">
-        <v>7.77001523971558</v>
+        <v>7.77001571655273</v>
       </c>
       <c r="H23" t="n">
         <v>2600</v>
@@ -1152,7 +1152,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G27" t="n">
-        <v>7.94527864456177</v>
+        <v>7.94527912139893</v>
       </c>
       <c r="H27" t="n">
         <v>15200</v>
@@ -1181,7 +1181,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G28" t="n">
-        <v>7.94527864456177</v>
+        <v>7.94527912139893</v>
       </c>
       <c r="H28" t="n">
         <v>8200</v>
@@ -1210,7 +1210,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G29" t="n">
-        <v>7.77001523971558</v>
+        <v>7.77001571655273</v>
       </c>
       <c r="H29" t="n">
         <v>9000</v>
@@ -1239,7 +1239,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G30" t="n">
-        <v>7.77001523971558</v>
+        <v>7.77001571655273</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
@@ -1384,7 +1384,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G35" t="n">
-        <v>8.0815954208374</v>
+        <v>8.08159446716309</v>
       </c>
       <c r="H35" t="n">
         <v>1800</v>
@@ -1442,7 +1442,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G37" t="n">
-        <v>8.0815954208374</v>
+        <v>8.08159446716309</v>
       </c>
       <c r="H37" t="n">
         <v>3400</v>
@@ -1471,7 +1471,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G38" t="n">
-        <v>8.17896270751953</v>
+        <v>8.17896366119385</v>
       </c>
       <c r="H38" t="n">
         <v>14400</v>
@@ -1529,7 +1529,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G40" t="n">
-        <v>8.29580593109131</v>
+        <v>8.29580688476562</v>
       </c>
       <c r="H40" t="n">
         <v>4400</v>
@@ -1558,7 +1558,7 @@
         <v>8.5</v>
       </c>
       <c r="G41" t="n">
-        <v>8.27633190155029</v>
+        <v>8.27633285522461</v>
       </c>
       <c r="H41" t="n">
         <v>1200</v>
@@ -1587,7 +1587,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G42" t="n">
-        <v>8.17896270751953</v>
+        <v>8.17896366119385</v>
       </c>
       <c r="H42" t="n">
         <v>800</v>
@@ -1935,7 +1935,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G54" t="n">
-        <v>8.78264904022217</v>
+        <v>8.78264999389648</v>
       </c>
       <c r="H54" t="n">
         <v>4600</v>
@@ -1964,7 +1964,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G55" t="n">
-        <v>8.86054420471191</v>
+        <v>8.86054515838623</v>
       </c>
       <c r="H55" t="n">
         <v>6400</v>
@@ -2051,7 +2051,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G58" t="n">
-        <v>8.66580677032471</v>
+        <v>8.66580581665039</v>
       </c>
       <c r="H58" t="n">
         <v>2000</v>
@@ -2080,7 +2080,7 @@
         <v>8.92000007629395</v>
       </c>
       <c r="G59" t="n">
-        <v>8.68528079986572</v>
+        <v>8.68527984619141</v>
       </c>
       <c r="H59" t="n">
         <v>800</v>
@@ -2167,7 +2167,7 @@
         <v>8.5</v>
       </c>
       <c r="G62" t="n">
-        <v>8.27633190155029</v>
+        <v>8.27633285522461</v>
       </c>
       <c r="H62" t="n">
         <v>1600</v>
@@ -2196,7 +2196,7 @@
         <v>8.5</v>
       </c>
       <c r="G63" t="n">
-        <v>8.27633190155029</v>
+        <v>8.27633285522461</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
@@ -2283,7 +2283,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G66" t="n">
-        <v>8.0815954208374</v>
+        <v>8.08159446716309</v>
       </c>
       <c r="H66" t="n">
         <v>200</v>
@@ -2312,7 +2312,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G67" t="n">
-        <v>7.90633153915405</v>
+        <v>7.90633106231689</v>
       </c>
       <c r="H67" t="n">
         <v>3800</v>
@@ -2370,7 +2370,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G69" t="n">
-        <v>7.94527864456177</v>
+        <v>7.94527912139893</v>
       </c>
       <c r="H69" t="n">
         <v>2800</v>
@@ -2457,7 +2457,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G72" t="n">
-        <v>7.94527864456177</v>
+        <v>7.94527912139893</v>
       </c>
       <c r="H72" t="n">
         <v>1000</v>
@@ -2544,7 +2544,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G75" t="n">
-        <v>8.0815954208374</v>
+        <v>8.08159446716309</v>
       </c>
       <c r="H75" t="n">
         <v>2600</v>
@@ -2573,7 +2573,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G76" t="n">
-        <v>7.75054216384888</v>
+        <v>7.75054168701172</v>
       </c>
       <c r="H76" t="n">
         <v>4200</v>
@@ -2660,7 +2660,7 @@
         <v>7.76000022888184</v>
       </c>
       <c r="G79" t="n">
-        <v>7.55580472946167</v>
+        <v>7.55580520629883</v>
       </c>
       <c r="H79" t="n">
         <v>200</v>
@@ -2718,7 +2718,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G81" t="n">
-        <v>7.65317296981812</v>
+        <v>7.65317344665527</v>
       </c>
       <c r="H81" t="n">
         <v>400</v>
@@ -2747,7 +2747,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G82" t="n">
-        <v>7.65317296981812</v>
+        <v>7.65317344665527</v>
       </c>
       <c r="H82" t="n">
         <v>0</v>
@@ -2834,7 +2834,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G85" t="n">
-        <v>7.82843637466431</v>
+        <v>7.82843685150146</v>
       </c>
       <c r="H85" t="n">
         <v>200</v>
@@ -2863,7 +2863,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G86" t="n">
-        <v>7.82843637466431</v>
+        <v>7.82843685150146</v>
       </c>
       <c r="H86" t="n">
         <v>200</v>
@@ -2892,7 +2892,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G87" t="n">
-        <v>7.80896377563477</v>
+        <v>7.80896329879761</v>
       </c>
       <c r="H87" t="n">
         <v>2000</v>
@@ -2921,7 +2921,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G88" t="n">
-        <v>7.82843637466431</v>
+        <v>7.82843685150146</v>
       </c>
       <c r="H88" t="n">
         <v>2400</v>
@@ -3008,7 +3008,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G91" t="n">
-        <v>7.63369989395142</v>
+        <v>7.63369941711426</v>
       </c>
       <c r="H91" t="n">
         <v>800</v>
@@ -3124,7 +3124,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G95" t="n">
-        <v>7.80896377563477</v>
+        <v>7.80896329879761</v>
       </c>
       <c r="H95" t="n">
         <v>200</v>
@@ -3153,7 +3153,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G96" t="n">
-        <v>7.80896377563477</v>
+        <v>7.80896329879761</v>
       </c>
       <c r="H96" t="n">
         <v>0</v>
@@ -3298,7 +3298,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G101" t="n">
-        <v>7.84791088104248</v>
+        <v>7.84791040420532</v>
       </c>
       <c r="H101" t="n">
         <v>200</v>
@@ -3414,7 +3414,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G105" t="n">
-        <v>7.94527864456177</v>
+        <v>7.94527912139893</v>
       </c>
       <c r="H105" t="n">
         <v>1000</v>
@@ -3559,7 +3559,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G110" t="n">
-        <v>7.47790908813477</v>
+        <v>7.47790956497192</v>
       </c>
       <c r="H110" t="n">
         <v>1600</v>
@@ -3588,7 +3588,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G111" t="n">
-        <v>7.47790908813477</v>
+        <v>7.47790956497192</v>
       </c>
       <c r="H111" t="n">
         <v>0</v>
@@ -3820,7 +3820,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G119" t="n">
-        <v>8.0815954208374</v>
+        <v>8.08159446716309</v>
       </c>
       <c r="H119" t="n">
         <v>400</v>
@@ -3849,7 +3849,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G120" t="n">
-        <v>8.0815954208374</v>
+        <v>8.08159446716309</v>
       </c>
       <c r="H120" t="n">
         <v>0</v>
@@ -3878,7 +3878,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G121" t="n">
-        <v>7.90633153915405</v>
+        <v>7.90633106231689</v>
       </c>
       <c r="H121" t="n">
         <v>600</v>
@@ -3907,7 +3907,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G122" t="n">
-        <v>7.90633153915405</v>
+        <v>7.90633106231689</v>
       </c>
       <c r="H122" t="n">
         <v>0</v>
@@ -3965,7 +3965,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G124" t="n">
-        <v>8.04264736175537</v>
+        <v>8.04264831542969</v>
       </c>
       <c r="H124" t="n">
         <v>1600</v>
@@ -4110,7 +4110,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G129" t="n">
-        <v>7.82843637466431</v>
+        <v>7.82843685150146</v>
       </c>
       <c r="H129" t="n">
         <v>200</v>
@@ -4139,7 +4139,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G130" t="n">
-        <v>7.82843637466431</v>
+        <v>7.82843685150146</v>
       </c>
       <c r="H130" t="n">
         <v>0</v>
@@ -4255,7 +4255,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G134" t="n">
-        <v>7.75054216384888</v>
+        <v>7.75054168701172</v>
       </c>
       <c r="H134" t="n">
         <v>200</v>
@@ -4284,7 +4284,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G135" t="n">
-        <v>7.94527864456177</v>
+        <v>7.94527912139893</v>
       </c>
       <c r="H135" t="n">
         <v>800</v>
@@ -4313,7 +4313,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G136" t="n">
-        <v>7.94527864456177</v>
+        <v>7.94527912139893</v>
       </c>
       <c r="H136" t="n">
         <v>0</v>
@@ -4458,7 +4458,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G141" t="n">
-        <v>7.82843637466431</v>
+        <v>7.82843685150146</v>
       </c>
       <c r="H141" t="n">
         <v>600</v>
@@ -4487,7 +4487,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G142" t="n">
-        <v>7.82843637466431</v>
+        <v>7.82843685150146</v>
       </c>
       <c r="H142" t="n">
         <v>0</v>
@@ -4835,7 +4835,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G154" t="n">
-        <v>7.45843601226807</v>
+        <v>7.45843553543091</v>
       </c>
       <c r="H154" t="n">
         <v>400</v>
@@ -4922,7 +4922,7 @@
         <v>7.78000020980835</v>
       </c>
       <c r="G157" t="n">
-        <v>7.57527875900269</v>
+        <v>7.57527828216553</v>
       </c>
       <c r="H157" t="n">
         <v>600</v>
@@ -5241,7 +5241,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G168" t="n">
-        <v>6.42632818222046</v>
+        <v>6.42632865905762</v>
       </c>
       <c r="H168" t="n">
         <v>15400</v>
@@ -5531,7 +5531,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G178" t="n">
-        <v>7.08843517303467</v>
+        <v>7.08843564987183</v>
       </c>
       <c r="H178" t="n">
         <v>1000</v>
@@ -5560,7 +5560,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G179" t="n">
-        <v>7.08843517303467</v>
+        <v>7.08843564987183</v>
       </c>
       <c r="H179" t="n">
         <v>200</v>
@@ -5589,7 +5589,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G180" t="n">
-        <v>6.83527660369873</v>
+        <v>6.83527708053589</v>
       </c>
       <c r="H180" t="n">
         <v>4400</v>
@@ -5647,7 +5647,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G182" t="n">
-        <v>6.73790836334229</v>
+        <v>6.73790788650513</v>
       </c>
       <c r="H182" t="n">
         <v>800</v>
@@ -6082,7 +6082,7 @@
         <v>7.78000020980835</v>
       </c>
       <c r="G197" t="n">
-        <v>7.57527875900269</v>
+        <v>7.57527828216553</v>
       </c>
       <c r="H197" t="n">
         <v>3000</v>
@@ -6140,7 +6140,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G199" t="n">
-        <v>7.28317260742188</v>
+        <v>7.28317213058472</v>
       </c>
       <c r="H199" t="n">
         <v>2200</v>
@@ -6169,7 +6169,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G200" t="n">
-        <v>7.12738275527954</v>
+        <v>7.1273832321167</v>
       </c>
       <c r="H200" t="n">
         <v>3000</v>
@@ -6227,7 +6227,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G202" t="n">
-        <v>6.54317045211792</v>
+        <v>6.54317092895508</v>
       </c>
       <c r="H202" t="n">
         <v>1600</v>
@@ -6256,7 +6256,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G203" t="n">
-        <v>6.54317045211792</v>
+        <v>6.54317092895508</v>
       </c>
       <c r="H203" t="n">
         <v>3000</v>
@@ -6285,7 +6285,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G204" t="n">
-        <v>6.54317045211792</v>
+        <v>6.54317092895508</v>
       </c>
       <c r="H204" t="n">
         <v>0</v>
@@ -6343,7 +6343,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G206" t="n">
-        <v>6.27053880691528</v>
+        <v>6.27053928375244</v>
       </c>
       <c r="H206" t="n">
         <v>10600</v>
@@ -6372,7 +6372,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G207" t="n">
-        <v>6.2900128364563</v>
+        <v>6.29001235961914</v>
       </c>
       <c r="H207" t="n">
         <v>2200</v>
@@ -6459,7 +6459,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G210" t="n">
-        <v>6.42632818222046</v>
+        <v>6.42632865905762</v>
       </c>
       <c r="H210" t="n">
         <v>4200</v>
@@ -6575,7 +6575,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G214" t="n">
-        <v>5.97843265533447</v>
+        <v>5.97843313217163</v>
       </c>
       <c r="H214" t="n">
         <v>7800</v>
@@ -6604,7 +6604,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G215" t="n">
-        <v>5.9200119972229</v>
+        <v>5.92001152038574</v>
       </c>
       <c r="H215" t="n">
         <v>10000</v>
@@ -6633,7 +6633,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G216" t="n">
-        <v>5.9200119972229</v>
+        <v>5.92001152038574</v>
       </c>
       <c r="H216" t="n">
         <v>8200</v>
@@ -6952,7 +6952,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G227" t="n">
-        <v>5.74474859237671</v>
+        <v>5.74474811553955</v>
       </c>
       <c r="H227" t="n">
         <v>200</v>
@@ -7010,7 +7010,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G229" t="n">
-        <v>5.62790632247925</v>
+        <v>5.62790584564209</v>
       </c>
       <c r="H229" t="n">
         <v>11400</v>
@@ -7097,7 +7097,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G232" t="n">
-        <v>5.74474859237671</v>
+        <v>5.74474811553955</v>
       </c>
       <c r="H232" t="n">
         <v>200</v>
@@ -7126,7 +7126,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G233" t="n">
-        <v>5.74474859237671</v>
+        <v>5.74474811553955</v>
       </c>
       <c r="H233" t="n">
         <v>5800</v>
@@ -7184,7 +7184,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G235" t="n">
-        <v>5.74474859237671</v>
+        <v>5.74474811553955</v>
       </c>
       <c r="H235" t="n">
         <v>600</v>
@@ -7213,7 +7213,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G236" t="n">
-        <v>5.74474859237671</v>
+        <v>5.74474811553955</v>
       </c>
       <c r="H236" t="n">
         <v>0</v>
@@ -7590,7 +7590,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G249" t="n">
-        <v>5.74474859237671</v>
+        <v>5.74474811553955</v>
       </c>
       <c r="H249" t="n">
         <v>400</v>
@@ -7648,7 +7648,7 @@
         <v>5.5</v>
       </c>
       <c r="G251" t="n">
-        <v>5.35527420043945</v>
+        <v>5.35527372360229</v>
       </c>
       <c r="H251" t="n">
         <v>3400</v>
@@ -7706,7 +7706,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G253" t="n">
-        <v>5.06316804885864</v>
+        <v>5.06316757202148</v>
       </c>
       <c r="H253" t="n">
         <v>4000</v>
@@ -7880,7 +7880,7 @@
         <v>5.5</v>
       </c>
       <c r="G259" t="n">
-        <v>5.35527420043945</v>
+        <v>5.35527372360229</v>
       </c>
       <c r="H259" t="n">
         <v>200</v>
@@ -7909,7 +7909,7 @@
         <v>5.25</v>
       </c>
       <c r="G260" t="n">
-        <v>5.11185264587402</v>
+        <v>5.11185216903687</v>
       </c>
       <c r="H260" t="n">
         <v>16800</v>
@@ -7938,7 +7938,7 @@
         <v>5</v>
       </c>
       <c r="G261" t="n">
-        <v>4.86843061447144</v>
+        <v>4.86843109130859</v>
       </c>
       <c r="H261" t="n">
         <v>10600</v>
@@ -7967,7 +7967,7 @@
         <v>5</v>
       </c>
       <c r="G262" t="n">
-        <v>4.86843061447144</v>
+        <v>4.86843109130859</v>
       </c>
       <c r="H262" t="n">
         <v>15600</v>
@@ -7996,7 +7996,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G263" t="n">
-        <v>5.25790500640869</v>
+        <v>5.25790548324585</v>
       </c>
       <c r="H263" t="n">
         <v>35800</v>
@@ -8054,7 +8054,7 @@
         <v>5.25</v>
       </c>
       <c r="G265" t="n">
-        <v>5.11185264587402</v>
+        <v>5.11185216903687</v>
       </c>
       <c r="H265" t="n">
         <v>77400</v>
@@ -8112,7 +8112,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G267" t="n">
-        <v>5.25790500640869</v>
+        <v>5.25790548324585</v>
       </c>
       <c r="H267" t="n">
         <v>400</v>
@@ -8141,7 +8141,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G268" t="n">
-        <v>5.4526424407959</v>
+        <v>5.45264196395874</v>
       </c>
       <c r="H268" t="n">
         <v>8200</v>
@@ -8228,7 +8228,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G271" t="n">
-        <v>5.4526424407959</v>
+        <v>5.45264196395874</v>
       </c>
       <c r="H271" t="n">
         <v>800</v>
@@ -8257,7 +8257,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G272" t="n">
-        <v>5.4526424407959</v>
+        <v>5.45264196395874</v>
       </c>
       <c r="H272" t="n">
         <v>200</v>
@@ -8315,7 +8315,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G274" t="n">
-        <v>5.55001068115234</v>
+        <v>5.5500111579895</v>
       </c>
       <c r="H274" t="n">
         <v>3200</v>
@@ -26069,6 +26069,35 @@
         <v>2200</v>
       </c>
       <c r="I886" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="887">
+      <c r="A887" t="s">
+        <v>9</v>
+      </c>
+      <c r="B887" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C887" t="n">
+        <v>6.40000009536743</v>
+      </c>
+      <c r="D887" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E887" t="n">
+        <v>6.19999980926514</v>
+      </c>
+      <c r="F887" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G887" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H887" t="n">
+        <v>3600</v>
+      </c>
+      <c r="I887" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ECMB.MI.xlsx
+++ b/data/ECMB.MI.xlsx
@@ -485,7 +485,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G4" t="n">
-        <v>8.25685787200928</v>
+        <v>8.25685882568359</v>
       </c>
       <c r="H4" t="n">
         <v>7000</v>
@@ -514,7 +514,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G5" t="n">
-        <v>8.17896366119385</v>
+        <v>8.17896270751953</v>
       </c>
       <c r="H5" t="n">
         <v>1400</v>
@@ -572,7 +572,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G7" t="n">
-        <v>8.08159446716309</v>
+        <v>8.0815954208374</v>
       </c>
       <c r="H7" t="n">
         <v>4200</v>
@@ -630,7 +630,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G9" t="n">
-        <v>8.17896366119385</v>
+        <v>8.17896270751953</v>
       </c>
       <c r="H9" t="n">
         <v>200</v>
@@ -659,7 +659,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G10" t="n">
-        <v>8.17896366119385</v>
+        <v>8.17896270751953</v>
       </c>
       <c r="H10" t="n">
         <v>3600</v>
@@ -688,7 +688,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G11" t="n">
-        <v>8.14001560211182</v>
+        <v>8.14001655578613</v>
       </c>
       <c r="H11" t="n">
         <v>200</v>
@@ -804,7 +804,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G15" t="n">
-        <v>7.82843685150146</v>
+        <v>7.82843637466431</v>
       </c>
       <c r="H15" t="n">
         <v>2600</v>
@@ -833,7 +833,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G16" t="n">
-        <v>7.90633106231689</v>
+        <v>7.90633153915405</v>
       </c>
       <c r="H16" t="n">
         <v>6400</v>
@@ -891,7 +891,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G18" t="n">
-        <v>7.94527912139893</v>
+        <v>7.94527864456177</v>
       </c>
       <c r="H18" t="n">
         <v>2600</v>
@@ -920,7 +920,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G19" t="n">
-        <v>7.94527912139893</v>
+        <v>7.94527864456177</v>
       </c>
       <c r="H19" t="n">
         <v>600</v>
@@ -1036,7 +1036,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G23" t="n">
-        <v>7.77001571655273</v>
+        <v>7.77001523971558</v>
       </c>
       <c r="H23" t="n">
         <v>2600</v>
@@ -1152,7 +1152,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G27" t="n">
-        <v>7.94527912139893</v>
+        <v>7.94527864456177</v>
       </c>
       <c r="H27" t="n">
         <v>15200</v>
@@ -1181,7 +1181,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G28" t="n">
-        <v>7.94527912139893</v>
+        <v>7.94527864456177</v>
       </c>
       <c r="H28" t="n">
         <v>8200</v>
@@ -1210,7 +1210,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G29" t="n">
-        <v>7.77001571655273</v>
+        <v>7.77001523971558</v>
       </c>
       <c r="H29" t="n">
         <v>9000</v>
@@ -1239,7 +1239,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G30" t="n">
-        <v>7.77001571655273</v>
+        <v>7.77001523971558</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
@@ -1384,7 +1384,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G35" t="n">
-        <v>8.08159446716309</v>
+        <v>8.0815954208374</v>
       </c>
       <c r="H35" t="n">
         <v>1800</v>
@@ -1442,7 +1442,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G37" t="n">
-        <v>8.08159446716309</v>
+        <v>8.0815954208374</v>
       </c>
       <c r="H37" t="n">
         <v>3400</v>
@@ -1471,7 +1471,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G38" t="n">
-        <v>8.17896366119385</v>
+        <v>8.17896270751953</v>
       </c>
       <c r="H38" t="n">
         <v>14400</v>
@@ -1529,7 +1529,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G40" t="n">
-        <v>8.29580688476562</v>
+        <v>8.29580593109131</v>
       </c>
       <c r="H40" t="n">
         <v>4400</v>
@@ -1558,7 +1558,7 @@
         <v>8.5</v>
       </c>
       <c r="G41" t="n">
-        <v>8.27633285522461</v>
+        <v>8.27633190155029</v>
       </c>
       <c r="H41" t="n">
         <v>1200</v>
@@ -1587,7 +1587,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G42" t="n">
-        <v>8.17896366119385</v>
+        <v>8.17896270751953</v>
       </c>
       <c r="H42" t="n">
         <v>800</v>
@@ -1935,7 +1935,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G54" t="n">
-        <v>8.78264999389648</v>
+        <v>8.78264904022217</v>
       </c>
       <c r="H54" t="n">
         <v>4600</v>
@@ -1964,7 +1964,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G55" t="n">
-        <v>8.86054515838623</v>
+        <v>8.86054420471191</v>
       </c>
       <c r="H55" t="n">
         <v>6400</v>
@@ -2051,7 +2051,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G58" t="n">
-        <v>8.66580581665039</v>
+        <v>8.66580677032471</v>
       </c>
       <c r="H58" t="n">
         <v>2000</v>
@@ -2080,7 +2080,7 @@
         <v>8.92000007629395</v>
       </c>
       <c r="G59" t="n">
-        <v>8.68527984619141</v>
+        <v>8.68528079986572</v>
       </c>
       <c r="H59" t="n">
         <v>800</v>
@@ -2167,7 +2167,7 @@
         <v>8.5</v>
       </c>
       <c r="G62" t="n">
-        <v>8.27633285522461</v>
+        <v>8.27633190155029</v>
       </c>
       <c r="H62" t="n">
         <v>1600</v>
@@ -2196,7 +2196,7 @@
         <v>8.5</v>
       </c>
       <c r="G63" t="n">
-        <v>8.27633285522461</v>
+        <v>8.27633190155029</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
@@ -2283,7 +2283,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G66" t="n">
-        <v>8.08159446716309</v>
+        <v>8.0815954208374</v>
       </c>
       <c r="H66" t="n">
         <v>200</v>
@@ -2312,7 +2312,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G67" t="n">
-        <v>7.90633106231689</v>
+        <v>7.90633153915405</v>
       </c>
       <c r="H67" t="n">
         <v>3800</v>
@@ -2370,7 +2370,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G69" t="n">
-        <v>7.94527912139893</v>
+        <v>7.94527864456177</v>
       </c>
       <c r="H69" t="n">
         <v>2800</v>
@@ -2457,7 +2457,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G72" t="n">
-        <v>7.94527912139893</v>
+        <v>7.94527864456177</v>
       </c>
       <c r="H72" t="n">
         <v>1000</v>
@@ -2544,7 +2544,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G75" t="n">
-        <v>8.08159446716309</v>
+        <v>8.0815954208374</v>
       </c>
       <c r="H75" t="n">
         <v>2600</v>
@@ -2573,7 +2573,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G76" t="n">
-        <v>7.75054168701172</v>
+        <v>7.75054216384888</v>
       </c>
       <c r="H76" t="n">
         <v>4200</v>
@@ -2660,7 +2660,7 @@
         <v>7.76000022888184</v>
       </c>
       <c r="G79" t="n">
-        <v>7.55580520629883</v>
+        <v>7.55580472946167</v>
       </c>
       <c r="H79" t="n">
         <v>200</v>
@@ -2718,7 +2718,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G81" t="n">
-        <v>7.65317344665527</v>
+        <v>7.65317296981812</v>
       </c>
       <c r="H81" t="n">
         <v>400</v>
@@ -2747,7 +2747,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G82" t="n">
-        <v>7.65317344665527</v>
+        <v>7.65317296981812</v>
       </c>
       <c r="H82" t="n">
         <v>0</v>
@@ -2834,7 +2834,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G85" t="n">
-        <v>7.82843685150146</v>
+        <v>7.82843637466431</v>
       </c>
       <c r="H85" t="n">
         <v>200</v>
@@ -2863,7 +2863,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G86" t="n">
-        <v>7.82843685150146</v>
+        <v>7.82843637466431</v>
       </c>
       <c r="H86" t="n">
         <v>200</v>
@@ -2892,7 +2892,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G87" t="n">
-        <v>7.80896329879761</v>
+        <v>7.80896377563477</v>
       </c>
       <c r="H87" t="n">
         <v>2000</v>
@@ -2921,7 +2921,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G88" t="n">
-        <v>7.82843685150146</v>
+        <v>7.82843637466431</v>
       </c>
       <c r="H88" t="n">
         <v>2400</v>
@@ -3008,7 +3008,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G91" t="n">
-        <v>7.63369941711426</v>
+        <v>7.63369989395142</v>
       </c>
       <c r="H91" t="n">
         <v>800</v>
@@ -3124,7 +3124,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G95" t="n">
-        <v>7.80896329879761</v>
+        <v>7.80896377563477</v>
       </c>
       <c r="H95" t="n">
         <v>200</v>
@@ -3153,7 +3153,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G96" t="n">
-        <v>7.80896329879761</v>
+        <v>7.80896377563477</v>
       </c>
       <c r="H96" t="n">
         <v>0</v>
@@ -3298,7 +3298,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G101" t="n">
-        <v>7.84791040420532</v>
+        <v>7.84791088104248</v>
       </c>
       <c r="H101" t="n">
         <v>200</v>
@@ -3414,7 +3414,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G105" t="n">
-        <v>7.94527912139893</v>
+        <v>7.94527864456177</v>
       </c>
       <c r="H105" t="n">
         <v>1000</v>
@@ -3559,7 +3559,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G110" t="n">
-        <v>7.47790956497192</v>
+        <v>7.47790908813477</v>
       </c>
       <c r="H110" t="n">
         <v>1600</v>
@@ -3588,7 +3588,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G111" t="n">
-        <v>7.47790956497192</v>
+        <v>7.47790908813477</v>
       </c>
       <c r="H111" t="n">
         <v>0</v>
@@ -3820,7 +3820,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G119" t="n">
-        <v>8.08159446716309</v>
+        <v>8.0815954208374</v>
       </c>
       <c r="H119" t="n">
         <v>400</v>
@@ -3849,7 +3849,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G120" t="n">
-        <v>8.08159446716309</v>
+        <v>8.0815954208374</v>
       </c>
       <c r="H120" t="n">
         <v>0</v>
@@ -3878,7 +3878,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G121" t="n">
-        <v>7.90633106231689</v>
+        <v>7.90633153915405</v>
       </c>
       <c r="H121" t="n">
         <v>600</v>
@@ -3907,7 +3907,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G122" t="n">
-        <v>7.90633106231689</v>
+        <v>7.90633153915405</v>
       </c>
       <c r="H122" t="n">
         <v>0</v>
@@ -3965,7 +3965,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G124" t="n">
-        <v>8.04264831542969</v>
+        <v>8.04264736175537</v>
       </c>
       <c r="H124" t="n">
         <v>1600</v>
@@ -4110,7 +4110,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G129" t="n">
-        <v>7.82843685150146</v>
+        <v>7.82843637466431</v>
       </c>
       <c r="H129" t="n">
         <v>200</v>
@@ -4139,7 +4139,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G130" t="n">
-        <v>7.82843685150146</v>
+        <v>7.82843637466431</v>
       </c>
       <c r="H130" t="n">
         <v>0</v>
@@ -4255,7 +4255,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G134" t="n">
-        <v>7.75054168701172</v>
+        <v>7.75054216384888</v>
       </c>
       <c r="H134" t="n">
         <v>200</v>
@@ -4284,7 +4284,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G135" t="n">
-        <v>7.94527912139893</v>
+        <v>7.94527864456177</v>
       </c>
       <c r="H135" t="n">
         <v>800</v>
@@ -4313,7 +4313,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G136" t="n">
-        <v>7.94527912139893</v>
+        <v>7.94527864456177</v>
       </c>
       <c r="H136" t="n">
         <v>0</v>
@@ -4458,7 +4458,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G141" t="n">
-        <v>7.82843685150146</v>
+        <v>7.82843637466431</v>
       </c>
       <c r="H141" t="n">
         <v>600</v>
@@ -4487,7 +4487,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G142" t="n">
-        <v>7.82843685150146</v>
+        <v>7.82843637466431</v>
       </c>
       <c r="H142" t="n">
         <v>0</v>
@@ -4835,7 +4835,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G154" t="n">
-        <v>7.45843553543091</v>
+        <v>7.45843601226807</v>
       </c>
       <c r="H154" t="n">
         <v>400</v>
@@ -4922,7 +4922,7 @@
         <v>7.78000020980835</v>
       </c>
       <c r="G157" t="n">
-        <v>7.57527828216553</v>
+        <v>7.57527875900269</v>
       </c>
       <c r="H157" t="n">
         <v>600</v>
@@ -5241,7 +5241,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G168" t="n">
-        <v>6.42632865905762</v>
+        <v>6.42632818222046</v>
       </c>
       <c r="H168" t="n">
         <v>15400</v>
@@ -5531,7 +5531,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G178" t="n">
-        <v>7.08843564987183</v>
+        <v>7.08843517303467</v>
       </c>
       <c r="H178" t="n">
         <v>1000</v>
@@ -5560,7 +5560,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G179" t="n">
-        <v>7.08843564987183</v>
+        <v>7.08843517303467</v>
       </c>
       <c r="H179" t="n">
         <v>200</v>
@@ -5589,7 +5589,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G180" t="n">
-        <v>6.83527708053589</v>
+        <v>6.83527660369873</v>
       </c>
       <c r="H180" t="n">
         <v>4400</v>
@@ -5647,7 +5647,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G182" t="n">
-        <v>6.73790788650513</v>
+        <v>6.73790836334229</v>
       </c>
       <c r="H182" t="n">
         <v>800</v>
@@ -6082,7 +6082,7 @@
         <v>7.78000020980835</v>
       </c>
       <c r="G197" t="n">
-        <v>7.57527828216553</v>
+        <v>7.57527875900269</v>
       </c>
       <c r="H197" t="n">
         <v>3000</v>
@@ -6140,7 +6140,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G199" t="n">
-        <v>7.28317213058472</v>
+        <v>7.28317260742188</v>
       </c>
       <c r="H199" t="n">
         <v>2200</v>
@@ -6169,7 +6169,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G200" t="n">
-        <v>7.1273832321167</v>
+        <v>7.12738275527954</v>
       </c>
       <c r="H200" t="n">
         <v>3000</v>
@@ -6227,7 +6227,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G202" t="n">
-        <v>6.54317092895508</v>
+        <v>6.54317045211792</v>
       </c>
       <c r="H202" t="n">
         <v>1600</v>
@@ -6256,7 +6256,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G203" t="n">
-        <v>6.54317092895508</v>
+        <v>6.54317045211792</v>
       </c>
       <c r="H203" t="n">
         <v>3000</v>
@@ -6285,7 +6285,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G204" t="n">
-        <v>6.54317092895508</v>
+        <v>6.54317045211792</v>
       </c>
       <c r="H204" t="n">
         <v>0</v>
@@ -6343,7 +6343,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G206" t="n">
-        <v>6.27053928375244</v>
+        <v>6.27053880691528</v>
       </c>
       <c r="H206" t="n">
         <v>10600</v>
@@ -6372,7 +6372,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G207" t="n">
-        <v>6.29001235961914</v>
+        <v>6.2900128364563</v>
       </c>
       <c r="H207" t="n">
         <v>2200</v>
@@ -6459,7 +6459,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G210" t="n">
-        <v>6.42632865905762</v>
+        <v>6.42632818222046</v>
       </c>
       <c r="H210" t="n">
         <v>4200</v>
@@ -6575,7 +6575,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G214" t="n">
-        <v>5.97843313217163</v>
+        <v>5.97843265533447</v>
       </c>
       <c r="H214" t="n">
         <v>7800</v>
@@ -6604,7 +6604,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G215" t="n">
-        <v>5.92001152038574</v>
+        <v>5.9200119972229</v>
       </c>
       <c r="H215" t="n">
         <v>10000</v>
@@ -6633,7 +6633,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G216" t="n">
-        <v>5.92001152038574</v>
+        <v>5.9200119972229</v>
       </c>
       <c r="H216" t="n">
         <v>8200</v>
@@ -6952,7 +6952,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G227" t="n">
-        <v>5.74474811553955</v>
+        <v>5.74474859237671</v>
       </c>
       <c r="H227" t="n">
         <v>200</v>
@@ -7010,7 +7010,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G229" t="n">
-        <v>5.62790584564209</v>
+        <v>5.62790632247925</v>
       </c>
       <c r="H229" t="n">
         <v>11400</v>
@@ -7097,7 +7097,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G232" t="n">
-        <v>5.74474811553955</v>
+        <v>5.74474859237671</v>
       </c>
       <c r="H232" t="n">
         <v>200</v>
@@ -7126,7 +7126,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G233" t="n">
-        <v>5.74474811553955</v>
+        <v>5.74474859237671</v>
       </c>
       <c r="H233" t="n">
         <v>5800</v>
@@ -7184,7 +7184,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G235" t="n">
-        <v>5.74474811553955</v>
+        <v>5.74474859237671</v>
       </c>
       <c r="H235" t="n">
         <v>600</v>
@@ -7213,7 +7213,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G236" t="n">
-        <v>5.74474811553955</v>
+        <v>5.74474859237671</v>
       </c>
       <c r="H236" t="n">
         <v>0</v>
@@ -7590,7 +7590,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G249" t="n">
-        <v>5.74474811553955</v>
+        <v>5.74474859237671</v>
       </c>
       <c r="H249" t="n">
         <v>400</v>
@@ -7648,7 +7648,7 @@
         <v>5.5</v>
       </c>
       <c r="G251" t="n">
-        <v>5.35527372360229</v>
+        <v>5.35527420043945</v>
       </c>
       <c r="H251" t="n">
         <v>3400</v>
@@ -7706,7 +7706,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G253" t="n">
-        <v>5.06316757202148</v>
+        <v>5.06316804885864</v>
       </c>
       <c r="H253" t="n">
         <v>4000</v>
@@ -7880,7 +7880,7 @@
         <v>5.5</v>
       </c>
       <c r="G259" t="n">
-        <v>5.35527372360229</v>
+        <v>5.35527420043945</v>
       </c>
       <c r="H259" t="n">
         <v>200</v>
@@ -7909,7 +7909,7 @@
         <v>5.25</v>
       </c>
       <c r="G260" t="n">
-        <v>5.11185216903687</v>
+        <v>5.11185264587402</v>
       </c>
       <c r="H260" t="n">
         <v>16800</v>
@@ -7938,7 +7938,7 @@
         <v>5</v>
       </c>
       <c r="G261" t="n">
-        <v>4.86843109130859</v>
+        <v>4.86843061447144</v>
       </c>
       <c r="H261" t="n">
         <v>10600</v>
@@ -7967,7 +7967,7 @@
         <v>5</v>
       </c>
       <c r="G262" t="n">
-        <v>4.86843109130859</v>
+        <v>4.86843061447144</v>
       </c>
       <c r="H262" t="n">
         <v>15600</v>
@@ -7996,7 +7996,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G263" t="n">
-        <v>5.25790548324585</v>
+        <v>5.25790500640869</v>
       </c>
       <c r="H263" t="n">
         <v>35800</v>
@@ -8054,7 +8054,7 @@
         <v>5.25</v>
       </c>
       <c r="G265" t="n">
-        <v>5.11185216903687</v>
+        <v>5.11185264587402</v>
       </c>
       <c r="H265" t="n">
         <v>77400</v>
@@ -8112,7 +8112,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G267" t="n">
-        <v>5.25790548324585</v>
+        <v>5.25790500640869</v>
       </c>
       <c r="H267" t="n">
         <v>400</v>
@@ -8141,7 +8141,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G268" t="n">
-        <v>5.45264196395874</v>
+        <v>5.4526424407959</v>
       </c>
       <c r="H268" t="n">
         <v>8200</v>
@@ -8228,7 +8228,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G271" t="n">
-        <v>5.45264196395874</v>
+        <v>5.4526424407959</v>
       </c>
       <c r="H271" t="n">
         <v>800</v>
@@ -8257,7 +8257,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G272" t="n">
-        <v>5.45264196395874</v>
+        <v>5.4526424407959</v>
       </c>
       <c r="H272" t="n">
         <v>200</v>
@@ -8315,7 +8315,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G274" t="n">
-        <v>5.5500111579895</v>
+        <v>5.55001068115234</v>
       </c>
       <c r="H274" t="n">
         <v>3200</v>
@@ -26098,6 +26098,35 @@
         <v>3600</v>
       </c>
       <c r="I887" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="888">
+      <c r="A888" t="s">
+        <v>9</v>
+      </c>
+      <c r="B888" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C888" t="n">
+        <v>6.40000009536743</v>
+      </c>
+      <c r="D888" t="n">
+        <v>6.40000009536743</v>
+      </c>
+      <c r="E888" t="n">
+        <v>6.40000009536743</v>
+      </c>
+      <c r="F888" t="n">
+        <v>6.40000009536743</v>
+      </c>
+      <c r="G888" t="n">
+        <v>6.40000009536743</v>
+      </c>
+      <c r="H888" t="n">
+        <v>1400</v>
+      </c>
+      <c r="I888" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ECMB.MI.xlsx
+++ b/data/ECMB.MI.xlsx
@@ -26130,6 +26130,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="889">
+      <c r="A889" t="s">
+        <v>9</v>
+      </c>
+      <c r="B889" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C889" t="n">
+        <v>6.40000009536743</v>
+      </c>
+      <c r="D889" t="n">
+        <v>6.40000009536743</v>
+      </c>
+      <c r="E889" t="n">
+        <v>6.40000009536743</v>
+      </c>
+      <c r="F889" t="n">
+        <v>6.40000009536743</v>
+      </c>
+      <c r="G889" t="n">
+        <v>6.40000009536743</v>
+      </c>
+      <c r="H889" t="n">
+        <v>400</v>
+      </c>
+      <c r="I889" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ECMB.MI.xlsx
+++ b/data/ECMB.MI.xlsx
@@ -26159,6 +26159,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="890">
+      <c r="A890" t="s">
+        <v>9</v>
+      </c>
+      <c r="B890" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C890" t="n">
+        <v>6.34999990463257</v>
+      </c>
+      <c r="D890" t="n">
+        <v>6.44999980926514</v>
+      </c>
+      <c r="E890" t="n">
+        <v>6.30000019073486</v>
+      </c>
+      <c r="F890" t="n">
+        <v>6.34999990463257</v>
+      </c>
+      <c r="G890" t="n">
+        <v>6.34999990463257</v>
+      </c>
+      <c r="H890" t="n">
+        <v>1400</v>
+      </c>
+      <c r="I890" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ECMB.MI.xlsx
+++ b/data/ECMB.MI.xlsx
@@ -485,7 +485,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G4" t="n">
-        <v>8.25685882568359</v>
+        <v>8.25685787200928</v>
       </c>
       <c r="H4" t="n">
         <v>7000</v>
@@ -514,7 +514,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G5" t="n">
-        <v>8.17896270751953</v>
+        <v>8.17896366119385</v>
       </c>
       <c r="H5" t="n">
         <v>1400</v>
@@ -572,7 +572,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G7" t="n">
-        <v>8.0815954208374</v>
+        <v>8.08159446716309</v>
       </c>
       <c r="H7" t="n">
         <v>4200</v>
@@ -630,7 +630,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G9" t="n">
-        <v>8.17896270751953</v>
+        <v>8.17896366119385</v>
       </c>
       <c r="H9" t="n">
         <v>200</v>
@@ -659,7 +659,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G10" t="n">
-        <v>8.17896270751953</v>
+        <v>8.17896366119385</v>
       </c>
       <c r="H10" t="n">
         <v>3600</v>
@@ -688,7 +688,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G11" t="n">
-        <v>8.14001655578613</v>
+        <v>8.14001560211182</v>
       </c>
       <c r="H11" t="n">
         <v>200</v>
@@ -804,7 +804,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G15" t="n">
-        <v>7.82843637466431</v>
+        <v>7.82843685150146</v>
       </c>
       <c r="H15" t="n">
         <v>2600</v>
@@ -833,7 +833,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G16" t="n">
-        <v>7.90633153915405</v>
+        <v>7.90633106231689</v>
       </c>
       <c r="H16" t="n">
         <v>6400</v>
@@ -891,7 +891,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G18" t="n">
-        <v>7.94527864456177</v>
+        <v>7.94527912139893</v>
       </c>
       <c r="H18" t="n">
         <v>2600</v>
@@ -920,7 +920,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G19" t="n">
-        <v>7.94527864456177</v>
+        <v>7.94527912139893</v>
       </c>
       <c r="H19" t="n">
         <v>600</v>
@@ -1036,7 +1036,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G23" t="n">
-        <v>7.77001523971558</v>
+        <v>7.77001571655273</v>
       </c>
       <c r="H23" t="n">
         <v>2600</v>
@@ -1152,7 +1152,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G27" t="n">
-        <v>7.94527864456177</v>
+        <v>7.94527912139893</v>
       </c>
       <c r="H27" t="n">
         <v>15200</v>
@@ -1181,7 +1181,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G28" t="n">
-        <v>7.94527864456177</v>
+        <v>7.94527912139893</v>
       </c>
       <c r="H28" t="n">
         <v>8200</v>
@@ -1210,7 +1210,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G29" t="n">
-        <v>7.77001523971558</v>
+        <v>7.77001571655273</v>
       </c>
       <c r="H29" t="n">
         <v>9000</v>
@@ -1239,7 +1239,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G30" t="n">
-        <v>7.77001523971558</v>
+        <v>7.77001571655273</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
@@ -1384,7 +1384,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G35" t="n">
-        <v>8.0815954208374</v>
+        <v>8.08159446716309</v>
       </c>
       <c r="H35" t="n">
         <v>1800</v>
@@ -1442,7 +1442,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G37" t="n">
-        <v>8.0815954208374</v>
+        <v>8.08159446716309</v>
       </c>
       <c r="H37" t="n">
         <v>3400</v>
@@ -1471,7 +1471,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G38" t="n">
-        <v>8.17896270751953</v>
+        <v>8.17896366119385</v>
       </c>
       <c r="H38" t="n">
         <v>14400</v>
@@ -1529,7 +1529,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G40" t="n">
-        <v>8.29580593109131</v>
+        <v>8.29580688476562</v>
       </c>
       <c r="H40" t="n">
         <v>4400</v>
@@ -1558,7 +1558,7 @@
         <v>8.5</v>
       </c>
       <c r="G41" t="n">
-        <v>8.27633190155029</v>
+        <v>8.27633285522461</v>
       </c>
       <c r="H41" t="n">
         <v>1200</v>
@@ -1587,7 +1587,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G42" t="n">
-        <v>8.17896270751953</v>
+        <v>8.17896366119385</v>
       </c>
       <c r="H42" t="n">
         <v>800</v>
@@ -1935,7 +1935,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G54" t="n">
-        <v>8.78264904022217</v>
+        <v>8.78264999389648</v>
       </c>
       <c r="H54" t="n">
         <v>4600</v>
@@ -1964,7 +1964,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G55" t="n">
-        <v>8.86054420471191</v>
+        <v>8.86054515838623</v>
       </c>
       <c r="H55" t="n">
         <v>6400</v>
@@ -2051,7 +2051,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G58" t="n">
-        <v>8.66580677032471</v>
+        <v>8.66580581665039</v>
       </c>
       <c r="H58" t="n">
         <v>2000</v>
@@ -2080,7 +2080,7 @@
         <v>8.92000007629395</v>
       </c>
       <c r="G59" t="n">
-        <v>8.68528079986572</v>
+        <v>8.68527984619141</v>
       </c>
       <c r="H59" t="n">
         <v>800</v>
@@ -2167,7 +2167,7 @@
         <v>8.5</v>
       </c>
       <c r="G62" t="n">
-        <v>8.27633190155029</v>
+        <v>8.27633285522461</v>
       </c>
       <c r="H62" t="n">
         <v>1600</v>
@@ -2196,7 +2196,7 @@
         <v>8.5</v>
       </c>
       <c r="G63" t="n">
-        <v>8.27633190155029</v>
+        <v>8.27633285522461</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
@@ -2283,7 +2283,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G66" t="n">
-        <v>8.0815954208374</v>
+        <v>8.08159446716309</v>
       </c>
       <c r="H66" t="n">
         <v>200</v>
@@ -2312,7 +2312,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G67" t="n">
-        <v>7.90633153915405</v>
+        <v>7.90633106231689</v>
       </c>
       <c r="H67" t="n">
         <v>3800</v>
@@ -2370,7 +2370,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G69" t="n">
-        <v>7.94527864456177</v>
+        <v>7.94527912139893</v>
       </c>
       <c r="H69" t="n">
         <v>2800</v>
@@ -2457,7 +2457,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G72" t="n">
-        <v>7.94527864456177</v>
+        <v>7.94527912139893</v>
       </c>
       <c r="H72" t="n">
         <v>1000</v>
@@ -2544,7 +2544,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G75" t="n">
-        <v>8.0815954208374</v>
+        <v>8.08159446716309</v>
       </c>
       <c r="H75" t="n">
         <v>2600</v>
@@ -2573,7 +2573,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G76" t="n">
-        <v>7.75054216384888</v>
+        <v>7.75054168701172</v>
       </c>
       <c r="H76" t="n">
         <v>4200</v>
@@ -2660,7 +2660,7 @@
         <v>7.76000022888184</v>
       </c>
       <c r="G79" t="n">
-        <v>7.55580472946167</v>
+        <v>7.55580520629883</v>
       </c>
       <c r="H79" t="n">
         <v>200</v>
@@ -2718,7 +2718,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G81" t="n">
-        <v>7.65317296981812</v>
+        <v>7.65317344665527</v>
       </c>
       <c r="H81" t="n">
         <v>400</v>
@@ -2747,7 +2747,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G82" t="n">
-        <v>7.65317296981812</v>
+        <v>7.65317344665527</v>
       </c>
       <c r="H82" t="n">
         <v>0</v>
@@ -2834,7 +2834,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G85" t="n">
-        <v>7.82843637466431</v>
+        <v>7.82843685150146</v>
       </c>
       <c r="H85" t="n">
         <v>200</v>
@@ -2863,7 +2863,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G86" t="n">
-        <v>7.82843637466431</v>
+        <v>7.82843685150146</v>
       </c>
       <c r="H86" t="n">
         <v>200</v>
@@ -2892,7 +2892,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G87" t="n">
-        <v>7.80896377563477</v>
+        <v>7.80896329879761</v>
       </c>
       <c r="H87" t="n">
         <v>2000</v>
@@ -2921,7 +2921,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G88" t="n">
-        <v>7.82843637466431</v>
+        <v>7.82843685150146</v>
       </c>
       <c r="H88" t="n">
         <v>2400</v>
@@ -3008,7 +3008,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G91" t="n">
-        <v>7.63369989395142</v>
+        <v>7.63369941711426</v>
       </c>
       <c r="H91" t="n">
         <v>800</v>
@@ -3124,7 +3124,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G95" t="n">
-        <v>7.80896377563477</v>
+        <v>7.80896329879761</v>
       </c>
       <c r="H95" t="n">
         <v>200</v>
@@ -3153,7 +3153,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G96" t="n">
-        <v>7.80896377563477</v>
+        <v>7.80896329879761</v>
       </c>
       <c r="H96" t="n">
         <v>0</v>
@@ -3298,7 +3298,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G101" t="n">
-        <v>7.84791088104248</v>
+        <v>7.84791040420532</v>
       </c>
       <c r="H101" t="n">
         <v>200</v>
@@ -3414,7 +3414,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G105" t="n">
-        <v>7.94527864456177</v>
+        <v>7.94527912139893</v>
       </c>
       <c r="H105" t="n">
         <v>1000</v>
@@ -3559,7 +3559,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G110" t="n">
-        <v>7.47790908813477</v>
+        <v>7.47790956497192</v>
       </c>
       <c r="H110" t="n">
         <v>1600</v>
@@ -3588,7 +3588,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G111" t="n">
-        <v>7.47790908813477</v>
+        <v>7.47790956497192</v>
       </c>
       <c r="H111" t="n">
         <v>0</v>
@@ -3820,7 +3820,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G119" t="n">
-        <v>8.0815954208374</v>
+        <v>8.08159446716309</v>
       </c>
       <c r="H119" t="n">
         <v>400</v>
@@ -3849,7 +3849,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G120" t="n">
-        <v>8.0815954208374</v>
+        <v>8.08159446716309</v>
       </c>
       <c r="H120" t="n">
         <v>0</v>
@@ -3878,7 +3878,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G121" t="n">
-        <v>7.90633153915405</v>
+        <v>7.90633106231689</v>
       </c>
       <c r="H121" t="n">
         <v>600</v>
@@ -3907,7 +3907,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G122" t="n">
-        <v>7.90633153915405</v>
+        <v>7.90633106231689</v>
       </c>
       <c r="H122" t="n">
         <v>0</v>
@@ -3965,7 +3965,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G124" t="n">
-        <v>8.04264736175537</v>
+        <v>8.04264831542969</v>
       </c>
       <c r="H124" t="n">
         <v>1600</v>
@@ -4110,7 +4110,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G129" t="n">
-        <v>7.82843637466431</v>
+        <v>7.82843685150146</v>
       </c>
       <c r="H129" t="n">
         <v>200</v>
@@ -4139,7 +4139,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G130" t="n">
-        <v>7.82843637466431</v>
+        <v>7.82843685150146</v>
       </c>
       <c r="H130" t="n">
         <v>0</v>
@@ -4255,7 +4255,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G134" t="n">
-        <v>7.75054216384888</v>
+        <v>7.75054168701172</v>
       </c>
       <c r="H134" t="n">
         <v>200</v>
@@ -4284,7 +4284,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G135" t="n">
-        <v>7.94527864456177</v>
+        <v>7.94527912139893</v>
       </c>
       <c r="H135" t="n">
         <v>800</v>
@@ -4313,7 +4313,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G136" t="n">
-        <v>7.94527864456177</v>
+        <v>7.94527912139893</v>
       </c>
       <c r="H136" t="n">
         <v>0</v>
@@ -4458,7 +4458,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G141" t="n">
-        <v>7.82843637466431</v>
+        <v>7.82843685150146</v>
       </c>
       <c r="H141" t="n">
         <v>600</v>
@@ -4487,7 +4487,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G142" t="n">
-        <v>7.82843637466431</v>
+        <v>7.82843685150146</v>
       </c>
       <c r="H142" t="n">
         <v>0</v>
@@ -4835,7 +4835,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G154" t="n">
-        <v>7.45843601226807</v>
+        <v>7.45843553543091</v>
       </c>
       <c r="H154" t="n">
         <v>400</v>
@@ -4922,7 +4922,7 @@
         <v>7.78000020980835</v>
       </c>
       <c r="G157" t="n">
-        <v>7.57527875900269</v>
+        <v>7.57527828216553</v>
       </c>
       <c r="H157" t="n">
         <v>600</v>
@@ -5241,7 +5241,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G168" t="n">
-        <v>6.42632818222046</v>
+        <v>6.42632865905762</v>
       </c>
       <c r="H168" t="n">
         <v>15400</v>
@@ -5531,7 +5531,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G178" t="n">
-        <v>7.08843517303467</v>
+        <v>7.08843564987183</v>
       </c>
       <c r="H178" t="n">
         <v>1000</v>
@@ -5560,7 +5560,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G179" t="n">
-        <v>7.08843517303467</v>
+        <v>7.08843564987183</v>
       </c>
       <c r="H179" t="n">
         <v>200</v>
@@ -5589,7 +5589,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G180" t="n">
-        <v>6.83527660369873</v>
+        <v>6.83527708053589</v>
       </c>
       <c r="H180" t="n">
         <v>4400</v>
@@ -5647,7 +5647,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G182" t="n">
-        <v>6.73790836334229</v>
+        <v>6.73790788650513</v>
       </c>
       <c r="H182" t="n">
         <v>800</v>
@@ -6082,7 +6082,7 @@
         <v>7.78000020980835</v>
       </c>
       <c r="G197" t="n">
-        <v>7.57527875900269</v>
+        <v>7.57527828216553</v>
       </c>
       <c r="H197" t="n">
         <v>3000</v>
@@ -6140,7 +6140,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G199" t="n">
-        <v>7.28317260742188</v>
+        <v>7.28317213058472</v>
       </c>
       <c r="H199" t="n">
         <v>2200</v>
@@ -6169,7 +6169,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G200" t="n">
-        <v>7.12738275527954</v>
+        <v>7.1273832321167</v>
       </c>
       <c r="H200" t="n">
         <v>3000</v>
@@ -6227,7 +6227,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G202" t="n">
-        <v>6.54317045211792</v>
+        <v>6.54317092895508</v>
       </c>
       <c r="H202" t="n">
         <v>1600</v>
@@ -6256,7 +6256,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G203" t="n">
-        <v>6.54317045211792</v>
+        <v>6.54317092895508</v>
       </c>
       <c r="H203" t="n">
         <v>3000</v>
@@ -6285,7 +6285,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G204" t="n">
-        <v>6.54317045211792</v>
+        <v>6.54317092895508</v>
       </c>
       <c r="H204" t="n">
         <v>0</v>
@@ -6343,7 +6343,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G206" t="n">
-        <v>6.27053880691528</v>
+        <v>6.27053928375244</v>
       </c>
       <c r="H206" t="n">
         <v>10600</v>
@@ -6372,7 +6372,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G207" t="n">
-        <v>6.2900128364563</v>
+        <v>6.29001235961914</v>
       </c>
       <c r="H207" t="n">
         <v>2200</v>
@@ -6459,7 +6459,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G210" t="n">
-        <v>6.42632818222046</v>
+        <v>6.42632865905762</v>
       </c>
       <c r="H210" t="n">
         <v>4200</v>
@@ -6575,7 +6575,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G214" t="n">
-        <v>5.97843265533447</v>
+        <v>5.97843313217163</v>
       </c>
       <c r="H214" t="n">
         <v>7800</v>
@@ -6604,7 +6604,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G215" t="n">
-        <v>5.9200119972229</v>
+        <v>5.92001152038574</v>
       </c>
       <c r="H215" t="n">
         <v>10000</v>
@@ -6633,7 +6633,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G216" t="n">
-        <v>5.9200119972229</v>
+        <v>5.92001152038574</v>
       </c>
       <c r="H216" t="n">
         <v>8200</v>
@@ -6952,7 +6952,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G227" t="n">
-        <v>5.74474859237671</v>
+        <v>5.74474811553955</v>
       </c>
       <c r="H227" t="n">
         <v>200</v>
@@ -7010,7 +7010,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G229" t="n">
-        <v>5.62790632247925</v>
+        <v>5.62790584564209</v>
       </c>
       <c r="H229" t="n">
         <v>11400</v>
@@ -7097,7 +7097,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G232" t="n">
-        <v>5.74474859237671</v>
+        <v>5.74474811553955</v>
       </c>
       <c r="H232" t="n">
         <v>200</v>
@@ -7126,7 +7126,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G233" t="n">
-        <v>5.74474859237671</v>
+        <v>5.74474811553955</v>
       </c>
       <c r="H233" t="n">
         <v>5800</v>
@@ -7184,7 +7184,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G235" t="n">
-        <v>5.74474859237671</v>
+        <v>5.74474811553955</v>
       </c>
       <c r="H235" t="n">
         <v>600</v>
@@ -7213,7 +7213,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G236" t="n">
-        <v>5.74474859237671</v>
+        <v>5.74474811553955</v>
       </c>
       <c r="H236" t="n">
         <v>0</v>
@@ -7590,7 +7590,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G249" t="n">
-        <v>5.74474859237671</v>
+        <v>5.74474811553955</v>
       </c>
       <c r="H249" t="n">
         <v>400</v>
@@ -7648,7 +7648,7 @@
         <v>5.5</v>
       </c>
       <c r="G251" t="n">
-        <v>5.35527420043945</v>
+        <v>5.35527372360229</v>
       </c>
       <c r="H251" t="n">
         <v>3400</v>
@@ -7706,7 +7706,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G253" t="n">
-        <v>5.06316804885864</v>
+        <v>5.06316757202148</v>
       </c>
       <c r="H253" t="n">
         <v>4000</v>
@@ -7880,7 +7880,7 @@
         <v>5.5</v>
       </c>
       <c r="G259" t="n">
-        <v>5.35527420043945</v>
+        <v>5.35527372360229</v>
       </c>
       <c r="H259" t="n">
         <v>200</v>
@@ -7909,7 +7909,7 @@
         <v>5.25</v>
       </c>
       <c r="G260" t="n">
-        <v>5.11185264587402</v>
+        <v>5.11185216903687</v>
       </c>
       <c r="H260" t="n">
         <v>16800</v>
@@ -7938,7 +7938,7 @@
         <v>5</v>
       </c>
       <c r="G261" t="n">
-        <v>4.86843061447144</v>
+        <v>4.86843109130859</v>
       </c>
       <c r="H261" t="n">
         <v>10600</v>
@@ -7967,7 +7967,7 @@
         <v>5</v>
       </c>
       <c r="G262" t="n">
-        <v>4.86843061447144</v>
+        <v>4.86843109130859</v>
       </c>
       <c r="H262" t="n">
         <v>15600</v>
@@ -7996,7 +7996,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G263" t="n">
-        <v>5.25790500640869</v>
+        <v>5.25790548324585</v>
       </c>
       <c r="H263" t="n">
         <v>35800</v>
@@ -8054,7 +8054,7 @@
         <v>5.25</v>
       </c>
       <c r="G265" t="n">
-        <v>5.11185264587402</v>
+        <v>5.11185216903687</v>
       </c>
       <c r="H265" t="n">
         <v>77400</v>
@@ -8112,7 +8112,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G267" t="n">
-        <v>5.25790500640869</v>
+        <v>5.25790548324585</v>
       </c>
       <c r="H267" t="n">
         <v>400</v>
@@ -8141,7 +8141,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G268" t="n">
-        <v>5.4526424407959</v>
+        <v>5.45264196395874</v>
       </c>
       <c r="H268" t="n">
         <v>8200</v>
@@ -8228,7 +8228,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G271" t="n">
-        <v>5.4526424407959</v>
+        <v>5.45264196395874</v>
       </c>
       <c r="H271" t="n">
         <v>800</v>
@@ -8257,7 +8257,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G272" t="n">
-        <v>5.4526424407959</v>
+        <v>5.45264196395874</v>
       </c>
       <c r="H272" t="n">
         <v>200</v>
@@ -8315,7 +8315,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G274" t="n">
-        <v>5.55001068115234</v>
+        <v>5.5500111579895</v>
       </c>
       <c r="H274" t="n">
         <v>3200</v>
@@ -26185,6 +26185,35 @@
         <v>1400</v>
       </c>
       <c r="I890" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="891">
+      <c r="A891" t="s">
+        <v>9</v>
+      </c>
+      <c r="B891" s="1" t="n">
+        <v>46325.3333333333</v>
+      </c>
+      <c r="C891" t="n">
+        <v>6.40000009536743</v>
+      </c>
+      <c r="D891" t="n">
+        <v>6.40000009536743</v>
+      </c>
+      <c r="E891" t="n">
+        <v>6.30000019073486</v>
+      </c>
+      <c r="F891" t="n">
+        <v>6.30000019073486</v>
+      </c>
+      <c r="G891" t="n">
+        <v>6.30000019073486</v>
+      </c>
+      <c r="H891" t="n">
+        <v>600</v>
+      </c>
+      <c r="I891" t="s">
         <v>9</v>
       </c>
     </row>
